--- a/etf_screener/data/top-performer-a (1).xlsx
+++ b/etf_screener/data/top-performer-a (1).xlsx
@@ -61,6 +61,690 @@
     <t>Total Return (1Y)</t>
   </si>
   <si>
+    <t>FLOW</t>
+  </si>
+  <si>
+    <t>Global X U.S. Cash Flow Kings 100 ETF</t>
+  </si>
+  <si>
+    <t>PIT</t>
+  </si>
+  <si>
+    <t>VanEck Commodity Strategy ETF</t>
+  </si>
+  <si>
+    <t>USCI</t>
+  </si>
+  <si>
+    <t>United States Commodity Index Fund, LP</t>
+  </si>
+  <si>
+    <t>SDCI</t>
+  </si>
+  <si>
+    <t>USCF SummerHaven Dynamic Commodity Strategy No K-1 Fund</t>
+  </si>
+  <si>
+    <t>HGER</t>
+  </si>
+  <si>
+    <t>Harbor Commodity All-Weather Strategy ETF</t>
+  </si>
+  <si>
+    <t>ONEO</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® Russell 1000 Momentum Focus ETF</t>
+  </si>
+  <si>
+    <t>VFLO</t>
+  </si>
+  <si>
+    <t>Victoryshares Free Cash Flow ETF</t>
+  </si>
+  <si>
+    <t>PJFV</t>
+  </si>
+  <si>
+    <t>PGIM Jennison Focused Value ETF</t>
+  </si>
+  <si>
+    <t>ROKT</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® S&amp;P Kensho Final Frontiers ETF</t>
+  </si>
+  <si>
+    <t>RAAX</t>
+  </si>
+  <si>
+    <t>VanEck Real Assets ETF</t>
+  </si>
+  <si>
+    <t>PVAL</t>
+  </si>
+  <si>
+    <t>Putnam Focused Large Cap Value ETF</t>
+  </si>
+  <si>
+    <t>ENFR</t>
+  </si>
+  <si>
+    <t>Alerian Energy Infrastructure ETF</t>
+  </si>
+  <si>
+    <t>FBT</t>
+  </si>
+  <si>
+    <t>First Trust NYSE Arca Biotechnology Index Fund</t>
+  </si>
+  <si>
+    <t>IAI</t>
+  </si>
+  <si>
+    <t>iShares U.S. Broker-Dealers &amp; Securities Exchanges ETF</t>
+  </si>
+  <si>
+    <t>GARP</t>
+  </si>
+  <si>
+    <t>iShares MSCI USA Quality GARP ETF</t>
+  </si>
+  <si>
+    <t>KOKU</t>
+  </si>
+  <si>
+    <t>Xtrackers MSCI Kokusai Equity ETF</t>
+  </si>
+  <si>
+    <t>SPVM</t>
+  </si>
+  <si>
+    <t>Invesco S&amp;P 500 Value with Momentum ETF</t>
+  </si>
+  <si>
+    <t>MOOD</t>
+  </si>
+  <si>
+    <t>Relative Sentiment Tactical Allocation ETF</t>
+  </si>
+  <si>
+    <t>HEWJ</t>
+  </si>
+  <si>
+    <t>iShares Currency Hedged MSCI Japan ETF</t>
+  </si>
+  <si>
+    <t>ESPO</t>
+  </si>
+  <si>
+    <t>VanEck Video Gaming and eSports ETF</t>
+  </si>
+  <si>
+    <t>BBCA</t>
+  </si>
+  <si>
+    <t>JPMorgan BetaBuilders Canada ETF</t>
+  </si>
+  <si>
+    <t>VNAM</t>
+  </si>
+  <si>
+    <t>Global X MSCI Vietnam ETF</t>
+  </si>
+  <si>
+    <t>IUSG</t>
+  </si>
+  <si>
+    <t>iShares Core S&amp;P U.S. Growth ETF</t>
+  </si>
+  <si>
+    <t>AAAU</t>
+  </si>
+  <si>
+    <t>Goldman Sachs Physical Gold ETF</t>
+  </si>
+  <si>
+    <t>FRTY</t>
+  </si>
+  <si>
+    <t>Alger Mid Cap 40 ETF</t>
+  </si>
+  <si>
+    <t>IAUM</t>
+  </si>
+  <si>
+    <t>iShares® Gold Trust Micro</t>
+  </si>
+  <si>
+    <t>IWD</t>
+  </si>
+  <si>
+    <t>iShares Russell 1000 Value ETF</t>
+  </si>
+  <si>
+    <t>DIVB</t>
+  </si>
+  <si>
+    <t>iShares Core Dividend ETF</t>
+  </si>
+  <si>
+    <t>GLDM</t>
+  </si>
+  <si>
+    <t>SPDR® Gold MiniShares</t>
+  </si>
+  <si>
+    <t>IDHQ</t>
+  </si>
+  <si>
+    <t>Invesco S&amp;P International Developed Quality ETF</t>
+  </si>
+  <si>
+    <t>KCE</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® S&amp;P® Capital Markets ETF</t>
+  </si>
+  <si>
+    <t>LGDS</t>
+  </si>
+  <si>
+    <t>JPMorgan Fundamental Data Science Large Growth ETF</t>
+  </si>
+  <si>
+    <t>FMDE</t>
+  </si>
+  <si>
+    <t>Fidelity Enhanced Mid Cap Core ETF</t>
+  </si>
+  <si>
+    <t>SEIV</t>
+  </si>
+  <si>
+    <t>SEI QiM U.S. Large Cap Value Active ETF</t>
+  </si>
+  <si>
+    <t>GCAD</t>
+  </si>
+  <si>
+    <t>Gabelli Commercial Aerospace &amp; Defense ETF</t>
+  </si>
+  <si>
+    <t>VFMF</t>
+  </si>
+  <si>
+    <t>Vanguard U.S. Multifactor ETF Shares</t>
+  </si>
+  <si>
+    <t>FGDL</t>
+  </si>
+  <si>
+    <t>Franklin Responsibly Sourced Gold ETF</t>
+  </si>
+  <si>
+    <t>AVGV</t>
+  </si>
+  <si>
+    <t>Avantis ALL Equity Markets Value ETF</t>
+  </si>
+  <si>
+    <t>DFUS</t>
+  </si>
+  <si>
+    <t>Dimensional U.S. Equity Market ETF</t>
+  </si>
+  <si>
+    <t>FLJH</t>
+  </si>
+  <si>
+    <t>Franklin FTSE Japan Hedged ETF</t>
+  </si>
+  <si>
+    <t>IVV</t>
+  </si>
+  <si>
+    <t>iShares Core S&amp;P 500 ETF</t>
+  </si>
+  <si>
+    <t>SPBC</t>
+  </si>
+  <si>
+    <t>Simplify US Equity PLUS Bitcoin Strategy ETF</t>
+  </si>
+  <si>
+    <t>BAR</t>
+  </si>
+  <si>
+    <t>GraniteShares Gold Trust</t>
+  </si>
+  <si>
+    <t>OVL</t>
+  </si>
+  <si>
+    <t>Overlay Shares Large Cap Equity ETF</t>
+  </si>
+  <si>
+    <t>JEPQ</t>
+  </si>
+  <si>
+    <t>JPMorgan Nasdaq Equity Premium Income ETF</t>
+  </si>
+  <si>
+    <t>BUFB</t>
+  </si>
+  <si>
+    <t>Innovator Laddered Allocation Buffer ETF</t>
+  </si>
+  <si>
+    <t>QLC</t>
+  </si>
+  <si>
+    <t>FlexShares US Quality Large Cap Index Fund</t>
+  </si>
+  <si>
+    <t>GDE</t>
+  </si>
+  <si>
+    <t>WisdomTree Efficient Gold Plus Equity Strategy Fund</t>
+  </si>
+  <si>
+    <t>FFLC</t>
+  </si>
+  <si>
+    <t>Fidelity Fundamental Large Cap Core ETF</t>
+  </si>
+  <si>
+    <t>GSWO</t>
+  </si>
+  <si>
+    <t>Goldman Sachs ActiveBeta World Equity ETF</t>
+  </si>
+  <si>
+    <t>AVUV</t>
+  </si>
+  <si>
+    <t>Avantis US Small Cap Value ETF</t>
+  </si>
+  <si>
+    <t>FEBT</t>
+  </si>
+  <si>
+    <t>Allianzim U.S. Equity Buffer10 Feb ETF</t>
+  </si>
+  <si>
+    <t>EPU</t>
+  </si>
+  <si>
+    <t>iShares MSCI Peru ETF</t>
+  </si>
+  <si>
+    <t>XBI</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® S&amp;P® Biotech ETF</t>
+  </si>
+  <si>
+    <t>XMVM</t>
+  </si>
+  <si>
+    <t>Invesco S&amp;P MidCap Value with Momentum ETF</t>
+  </si>
+  <si>
+    <t>HEZU</t>
+  </si>
+  <si>
+    <t>iShares Currency Hedged MSCI Eurozone ETF</t>
+  </si>
+  <si>
+    <t>AVMA</t>
+  </si>
+  <si>
+    <t>Avantis Moderate Allocation ETF</t>
+  </si>
+  <si>
+    <t>BUFR</t>
+  </si>
+  <si>
+    <t>FT Vest Laddered Buffer ETF</t>
+  </si>
+  <si>
+    <t>ESGG</t>
+  </si>
+  <si>
+    <t>FlexShares STOXX Global ESG Select Index Fund</t>
+  </si>
+  <si>
+    <t>IJK</t>
+  </si>
+  <si>
+    <t>iShares S&amp;P Mid-Cap 400 Growth ETF</t>
+  </si>
+  <si>
+    <t>IMCG</t>
+  </si>
+  <si>
+    <t>iShares Morningstar Mid-Cap Growth ETF</t>
+  </si>
+  <si>
+    <t>DFSV</t>
+  </si>
+  <si>
+    <t>Dimensional US Small Cap Value ETF</t>
+  </si>
+  <si>
+    <t>FWD</t>
+  </si>
+  <si>
+    <t>AB Disruptors ETF</t>
+  </si>
+  <si>
+    <t>MART</t>
+  </si>
+  <si>
+    <t>Allianzim U.S. Equity Buffer10 Mar ETF</t>
+  </si>
+  <si>
+    <t>EWP</t>
+  </si>
+  <si>
+    <t>iShares MSCI Spain ETF</t>
+  </si>
+  <si>
+    <t>BUL</t>
+  </si>
+  <si>
+    <t>Pacer US Cash Cows Growth ETF</t>
+  </si>
+  <si>
+    <t>QQQJ</t>
+  </si>
+  <si>
+    <t>Invesco NASDAQ Next Gen 100 ETF</t>
+  </si>
+  <si>
+    <t>IYW</t>
+  </si>
+  <si>
+    <t>iShares U.S. Technology ETF</t>
+  </si>
+  <si>
+    <t>ONEQ</t>
+  </si>
+  <si>
+    <t>Fidelity Nasdaq Composite Index ETF</t>
+  </si>
+  <si>
+    <t>AVGE</t>
+  </si>
+  <si>
+    <t>Avantis All Equity Markets ETF</t>
+  </si>
+  <si>
+    <t>EWI</t>
+  </si>
+  <si>
+    <t>iShares MSCI Italy ETF</t>
+  </si>
+  <si>
+    <t>AVDV</t>
+  </si>
+  <si>
+    <t>Avantis International Small Cap Value ETF</t>
+  </si>
+  <si>
+    <t>DBEF</t>
+  </si>
+  <si>
+    <t>Xtrackers MSCI EAFE Hedged Equity ETF</t>
+  </si>
+  <si>
+    <t>GVAL</t>
+  </si>
+  <si>
+    <t>Cambria Global Value ETF</t>
+  </si>
+  <si>
+    <t>SMLF</t>
+  </si>
+  <si>
+    <t>iShares U.S. Small-Cap Equity Factor ETF</t>
+  </si>
+  <si>
+    <t>HEFA</t>
+  </si>
+  <si>
+    <t>iShares Currency Hedged MSCI EAFE ETF</t>
+  </si>
+  <si>
+    <t>AOR</t>
+  </si>
+  <si>
+    <t>iShares Core 60/40 Balanced Allocation ETF</t>
+  </si>
+  <si>
+    <t>HAWX</t>
+  </si>
+  <si>
+    <t>iShares Currency Hedged MSCI ACWI ex U.S. ETF</t>
+  </si>
+  <si>
+    <t>FIDU</t>
+  </si>
+  <si>
+    <t>Fidelity MSCI Industrials Index ETF</t>
+  </si>
+  <si>
+    <t>AOA</t>
+  </si>
+  <si>
+    <t>iShares Core 80/20 Aggressive Allocation ETF</t>
+  </si>
+  <si>
+    <t>IOO</t>
+  </si>
+  <si>
+    <t>iShares Global 100 ETF</t>
+  </si>
+  <si>
+    <t>SDVY</t>
+  </si>
+  <si>
+    <t>First Trust SMID Cap Rising Dividend Achievers ETF</t>
+  </si>
+  <si>
+    <t>XTL</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® S&amp;P® Telecom ETF</t>
+  </si>
+  <si>
+    <t>PRN</t>
+  </si>
+  <si>
+    <t>Invesco Dorsey Wright Industrials Momentum ETF</t>
+  </si>
+  <si>
+    <t>EUFN</t>
+  </si>
+  <si>
+    <t>iShares MSCI Europe Financials ETF</t>
+  </si>
+  <si>
+    <t>SEIM</t>
+  </si>
+  <si>
+    <t>SEI QiM U.S. Large Cap Momentum Active ETF</t>
+  </si>
+  <si>
+    <t>PAVE</t>
+  </si>
+  <si>
+    <t>Global X U.S. Infrastructure Development ETF</t>
+  </si>
+  <si>
+    <t>VIS</t>
+  </si>
+  <si>
+    <t>Vanguard Industrials Index Fund ETF Shares</t>
+  </si>
+  <si>
+    <t>SDY</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® S&amp;P® Dividend ETF</t>
+  </si>
+  <si>
+    <t>HSCZ</t>
+  </si>
+  <si>
+    <t>iShares Currency Hedged MSCI EAFE Small-Cap ETF</t>
+  </si>
+  <si>
+    <t>IFRA</t>
+  </si>
+  <si>
+    <t>iShares U.S. Infrastructure ETF</t>
+  </si>
+  <si>
+    <t>FLTW</t>
+  </si>
+  <si>
+    <t>Franklin FTSE Taiwan ETF</t>
+  </si>
+  <si>
+    <t>AVNM</t>
+  </si>
+  <si>
+    <t>Avantis All International Markets Equity ETF</t>
+  </si>
+  <si>
+    <t>DFIV</t>
+  </si>
+  <si>
+    <t>Dimensional International Value ETF</t>
+  </si>
+  <si>
+    <t>IXG</t>
+  </si>
+  <si>
+    <t>iShares Global Financials ETF</t>
+  </si>
+  <si>
+    <t>SAMT</t>
+  </si>
+  <si>
+    <t>Strategas Macro Thematic Opportunities ETF</t>
+  </si>
+  <si>
+    <t>FTEC</t>
+  </si>
+  <si>
+    <t>Fidelity MSCI Information Technology Index ETF</t>
+  </si>
+  <si>
+    <t>CHPS</t>
+  </si>
+  <si>
+    <t>Xtrackers Semiconductor Select Equity ETF</t>
+  </si>
+  <si>
+    <t>XSMO</t>
+  </si>
+  <si>
+    <t>Invesco S&amp;P SmallCap Momentum ETF</t>
+  </si>
+  <si>
+    <t>DISV</t>
+  </si>
+  <si>
+    <t>Dimensional International Small Cap Value ETF</t>
+  </si>
+  <si>
+    <t>FGD</t>
+  </si>
+  <si>
+    <t>First Trust Dow Jones Global Select Dividend Index Fund</t>
+  </si>
+  <si>
+    <t>VDC</t>
+  </si>
+  <si>
+    <t>Vanguard Consumer Staples Index Fund ETF Shares</t>
+  </si>
+  <si>
+    <t>PXF</t>
+  </si>
+  <si>
+    <t>Invesco RAFI Developed Markets ex-U.S. ETF</t>
+  </si>
+  <si>
+    <t>FFSM</t>
+  </si>
+  <si>
+    <t>Fidelity Fundamental Small-Mid Cap ETF</t>
+  </si>
+  <si>
+    <t>FIVA</t>
+  </si>
+  <si>
+    <t>Fidelity International Value Factor ETF</t>
+  </si>
+  <si>
+    <t>USVM</t>
+  </si>
+  <si>
+    <t>VictoryShares US Small Mid Cap Value Momentum ETF</t>
+  </si>
+  <si>
+    <t>HEEM</t>
+  </si>
+  <si>
+    <t>iShares Currency Hedged MSCI Emerging Markets ETF</t>
+  </si>
+  <si>
+    <t>AVDS</t>
+  </si>
+  <si>
+    <t>Avantis International Small Cap Equity ETF</t>
+  </si>
+  <si>
+    <t>WDIV</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® S&amp;P® Global Dividend ETF</t>
+  </si>
+  <si>
+    <t>BKSE</t>
+  </si>
+  <si>
+    <t>BNY Mellon US Small Cap Core Equity ETF</t>
+  </si>
+  <si>
+    <t>EWT</t>
+  </si>
+  <si>
+    <t>iShares MSCI Taiwan ETF</t>
+  </si>
+  <si>
+    <t>ISVL</t>
+  </si>
+  <si>
+    <t>iShares International Developed Small Cap Value Factor ETF</t>
+  </si>
+  <si>
+    <t>IDEQ</t>
+  </si>
+  <si>
+    <t>Lazard International Dynamic Equity ETF</t>
+  </si>
+  <si>
+    <t>FDD</t>
+  </si>
+  <si>
+    <t>First Trust STOXX® European Select Dividend Index Fund</t>
+  </si>
+  <si>
     <t>RING</t>
   </si>
   <si>
@@ -73,28 +757,22 @@
     <t>Global X Uranium ETF</t>
   </si>
   <si>
-    <t>FBT</t>
-  </si>
-  <si>
-    <t>First Trust NYSE Arca Biotechnology Index Fund</t>
-  </si>
-  <si>
-    <t>ESPO</t>
-  </si>
-  <si>
-    <t>VanEck Video Gaming and eSports ETF</t>
-  </si>
-  <si>
-    <t>GDE</t>
-  </si>
-  <si>
-    <t>WisdomTree Efficient Gold Plus Equity Strategy Fund</t>
-  </si>
-  <si>
-    <t>BUL</t>
-  </si>
-  <si>
-    <t>Pacer US Cash Cows Growth ETF</t>
+    <t>WELD</t>
+  </si>
+  <si>
+    <t>Tema U.S. Manufacturing &amp; Reshoring ETF</t>
+  </si>
+  <si>
+    <t>SMH</t>
+  </si>
+  <si>
+    <t>VanEck Semiconductor ETF</t>
+  </si>
+  <si>
+    <t>DTCR</t>
+  </si>
+  <si>
+    <t>Global X Data Center &amp; Digital Infrastructure ETF</t>
   </si>
   <si>
     <t>SOXQ</t>
@@ -103,706 +781,28 @@
     <t>Invesco PHLX Semiconductor ETF</t>
   </si>
   <si>
-    <t>QQQJ</t>
-  </si>
-  <si>
-    <t>Invesco NASDAQ Next Gen 100 ETF</t>
-  </si>
-  <si>
-    <t>FGDL</t>
-  </si>
-  <si>
-    <t>Franklin Responsibly Sourced Gold ETF</t>
-  </si>
-  <si>
-    <t>BAR</t>
-  </si>
-  <si>
-    <t>GraniteShares Gold Trust</t>
-  </si>
-  <si>
-    <t>GLDM</t>
-  </si>
-  <si>
-    <t>SPDR® Gold MiniShares</t>
-  </si>
-  <si>
-    <t>IAUM</t>
-  </si>
-  <si>
-    <t>iShares® Gold Trust Micro</t>
-  </si>
-  <si>
-    <t>VFLO</t>
-  </si>
-  <si>
-    <t>Victoryshares Free Cash Flow ETF</t>
-  </si>
-  <si>
-    <t>AAAU</t>
-  </si>
-  <si>
-    <t>Goldman Sachs Physical Gold ETF</t>
-  </si>
-  <si>
-    <t>SMH</t>
-  </si>
-  <si>
-    <t>VanEck Semiconductor ETF</t>
-  </si>
-  <si>
-    <t>IJK</t>
-  </si>
-  <si>
-    <t>iShares S&amp;P Mid-Cap 400 Growth ETF</t>
-  </si>
-  <si>
-    <t>ONEO</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® Russell 1000 Momentum Focus ETF</t>
-  </si>
-  <si>
-    <t>XBI</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® S&amp;P® Biotech ETF</t>
-  </si>
-  <si>
-    <t>FLOW</t>
-  </si>
-  <si>
-    <t>Global X U.S. Cash Flow Kings 100 ETF</t>
-  </si>
-  <si>
-    <t>FTEC</t>
-  </si>
-  <si>
-    <t>Fidelity MSCI Information Technology Index ETF</t>
-  </si>
-  <si>
-    <t>IMCG</t>
-  </si>
-  <si>
-    <t>iShares Morningstar Mid-Cap Growth ETF</t>
-  </si>
-  <si>
-    <t>EPU</t>
-  </si>
-  <si>
-    <t>iShares MSCI Peru ETF</t>
-  </si>
-  <si>
-    <t>CHPS</t>
-  </si>
-  <si>
-    <t>Xtrackers Semiconductor Select Equity ETF</t>
-  </si>
-  <si>
-    <t>ROKT</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® S&amp;P Kensho Final Frontiers ETF</t>
-  </si>
-  <si>
-    <t>SMLF</t>
-  </si>
-  <si>
-    <t>iShares U.S. Small-Cap Equity Factor ETF</t>
-  </si>
-  <si>
-    <t>FRTY</t>
-  </si>
-  <si>
-    <t>Alger Mid Cap 40 ETF</t>
-  </si>
-  <si>
-    <t>IYW</t>
-  </si>
-  <si>
-    <t>iShares U.S. Technology ETF</t>
-  </si>
-  <si>
-    <t>IDHQ</t>
-  </si>
-  <si>
-    <t>Invesco S&amp;P International Developed Quality ETF</t>
-  </si>
-  <si>
-    <t>AVDV</t>
-  </si>
-  <si>
-    <t>Avantis International Small Cap Value ETF</t>
-  </si>
-  <si>
-    <t>ONEQ</t>
-  </si>
-  <si>
-    <t>Fidelity Nasdaq Composite Index ETF</t>
-  </si>
-  <si>
-    <t>FMDE</t>
-  </si>
-  <si>
-    <t>Fidelity Enhanced Mid Cap Core ETF</t>
-  </si>
-  <si>
-    <t>FWD</t>
-  </si>
-  <si>
-    <t>AB Disruptors ETF</t>
-  </si>
-  <si>
-    <t>IDEQ</t>
-  </si>
-  <si>
-    <t>Lazard International Dynamic Equity ETF</t>
-  </si>
-  <si>
-    <t>AVDS</t>
-  </si>
-  <si>
-    <t>Avantis International Small Cap Equity ETF</t>
-  </si>
-  <si>
-    <t>FLJH</t>
-  </si>
-  <si>
-    <t>Franklin FTSE Japan Hedged ETF</t>
-  </si>
-  <si>
-    <t>DTCR</t>
-  </si>
-  <si>
-    <t>Global X Data Center &amp; Digital Infrastructure ETF</t>
+    <t>USRT</t>
+  </si>
+  <si>
+    <t>iShares Core U.S. REIT ETF</t>
+  </si>
+  <si>
+    <t>BBRE</t>
+  </si>
+  <si>
+    <t>JPMorgan BetaBuilders MSCI U.S. REIT ETF</t>
+  </si>
+  <si>
+    <t>RWR</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® Dow Jones® REIT ETF</t>
   </si>
   <si>
     <t>EWJV</t>
   </si>
   <si>
     <t>iShares MSCI Japan Value ETF</t>
-  </si>
-  <si>
-    <t>DISV</t>
-  </si>
-  <si>
-    <t>Dimensional International Small Cap Value ETF</t>
-  </si>
-  <si>
-    <t>HEWJ</t>
-  </si>
-  <si>
-    <t>iShares Currency Hedged MSCI Japan ETF</t>
-  </si>
-  <si>
-    <t>AVNM</t>
-  </si>
-  <si>
-    <t>Avantis All International Markets Equity ETF</t>
-  </si>
-  <si>
-    <t>EWT</t>
-  </si>
-  <si>
-    <t>iShares MSCI Taiwan ETF</t>
-  </si>
-  <si>
-    <t>BKSE</t>
-  </si>
-  <si>
-    <t>BNY Mellon US Small Cap Core Equity ETF</t>
-  </si>
-  <si>
-    <t>FFSM</t>
-  </si>
-  <si>
-    <t>Fidelity Fundamental Small-Mid Cap ETF</t>
-  </si>
-  <si>
-    <t>GARP</t>
-  </si>
-  <si>
-    <t>iShares MSCI USA Quality GARP ETF</t>
-  </si>
-  <si>
-    <t>BBCA</t>
-  </si>
-  <si>
-    <t>JPMorgan BetaBuilders Canada ETF</t>
-  </si>
-  <si>
-    <t>PXF</t>
-  </si>
-  <si>
-    <t>Invesco RAFI Developed Markets ex-U.S. ETF</t>
-  </si>
-  <si>
-    <t>WDIV</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® S&amp;P® Global Dividend ETF</t>
-  </si>
-  <si>
-    <t>HGER</t>
-  </si>
-  <si>
-    <t>Harbor Commodity All-Weather Strategy ETF</t>
-  </si>
-  <si>
-    <t>RAAX</t>
-  </si>
-  <si>
-    <t>VanEck Real Assets ETF</t>
-  </si>
-  <si>
-    <t>HEFA</t>
-  </si>
-  <si>
-    <t>iShares Currency Hedged MSCI EAFE ETF</t>
-  </si>
-  <si>
-    <t>FIVA</t>
-  </si>
-  <si>
-    <t>Fidelity International Value Factor ETF</t>
-  </si>
-  <si>
-    <t>ESGG</t>
-  </si>
-  <si>
-    <t>FlexShares STOXX Global ESG Select Index Fund</t>
-  </si>
-  <si>
-    <t>VFMF</t>
-  </si>
-  <si>
-    <t>Vanguard U.S. Multifactor ETF Shares</t>
-  </si>
-  <si>
-    <t>FLTW</t>
-  </si>
-  <si>
-    <t>Franklin FTSE Taiwan ETF</t>
-  </si>
-  <si>
-    <t>GSWO</t>
-  </si>
-  <si>
-    <t>Goldman Sachs ActiveBeta World Equity ETF</t>
-  </si>
-  <si>
-    <t>ISVL</t>
-  </si>
-  <si>
-    <t>iShares International Developed Small Cap Value Factor ETF</t>
-  </si>
-  <si>
-    <t>HAWX</t>
-  </si>
-  <si>
-    <t>iShares Currency Hedged MSCI ACWI ex U.S. ETF</t>
-  </si>
-  <si>
-    <t>FDD</t>
-  </si>
-  <si>
-    <t>First Trust STOXX® European Select Dividend Index Fund</t>
-  </si>
-  <si>
-    <t>FGD</t>
-  </si>
-  <si>
-    <t>First Trust Dow Jones Global Select Dividend Index Fund</t>
-  </si>
-  <si>
-    <t>SPBC</t>
-  </si>
-  <si>
-    <t>Simplify US Equity PLUS Bitcoin Strategy ETF</t>
-  </si>
-  <si>
-    <t>SEIV</t>
-  </si>
-  <si>
-    <t>SEI QiM U.S. Large Cap Value Active ETF</t>
-  </si>
-  <si>
-    <t>HEEM</t>
-  </si>
-  <si>
-    <t>iShares Currency Hedged MSCI Emerging Markets ETF</t>
-  </si>
-  <si>
-    <t>IUSG</t>
-  </si>
-  <si>
-    <t>iShares Core S&amp;P U.S. Growth ETF</t>
-  </si>
-  <si>
-    <t>DIVB</t>
-  </si>
-  <si>
-    <t>iShares Core Dividend ETF</t>
-  </si>
-  <si>
-    <t>GCAD</t>
-  </si>
-  <si>
-    <t>Gabelli Commercial Aerospace &amp; Defense ETF</t>
-  </si>
-  <si>
-    <t>LGDS</t>
-  </si>
-  <si>
-    <t>JPMorgan Fundamental Data Science Large Growth ETF</t>
-  </si>
-  <si>
-    <t>DFUS</t>
-  </si>
-  <si>
-    <t>Dimensional U.S. Equity Market ETF</t>
-  </si>
-  <si>
-    <t>AOA</t>
-  </si>
-  <si>
-    <t>iShares Core 80/20 Aggressive Allocation ETF</t>
-  </si>
-  <si>
-    <t>SEIM</t>
-  </si>
-  <si>
-    <t>SEI QiM U.S. Large Cap Momentum Active ETF</t>
-  </si>
-  <si>
-    <t>OVL</t>
-  </si>
-  <si>
-    <t>Overlay Shares Large Cap Equity ETF</t>
-  </si>
-  <si>
-    <t>JEPQ</t>
-  </si>
-  <si>
-    <t>JPMorgan Nasdaq Equity Premium Income ETF</t>
-  </si>
-  <si>
-    <t>IOO</t>
-  </si>
-  <si>
-    <t>iShares Global 100 ETF</t>
-  </si>
-  <si>
-    <t>QLC</t>
-  </si>
-  <si>
-    <t>FlexShares US Quality Large Cap Index Fund</t>
-  </si>
-  <si>
-    <t>SDY</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® S&amp;P® Dividend ETF</t>
-  </si>
-  <si>
-    <t>DBEF</t>
-  </si>
-  <si>
-    <t>Xtrackers MSCI EAFE Hedged Equity ETF</t>
-  </si>
-  <si>
-    <t>IAI</t>
-  </si>
-  <si>
-    <t>iShares U.S. Broker-Dealers &amp; Securities Exchanges ETF</t>
-  </si>
-  <si>
-    <t>EUFN</t>
-  </si>
-  <si>
-    <t>iShares MSCI Europe Financials ETF</t>
-  </si>
-  <si>
-    <t>IVV</t>
-  </si>
-  <si>
-    <t>iShares Core S&amp;P 500 ETF</t>
-  </si>
-  <si>
-    <t>PAVE</t>
-  </si>
-  <si>
-    <t>Global X U.S. Infrastructure Development ETF</t>
-  </si>
-  <si>
-    <t>EWP</t>
-  </si>
-  <si>
-    <t>iShares MSCI Spain ETF</t>
-  </si>
-  <si>
-    <t>AOR</t>
-  </si>
-  <si>
-    <t>iShares Core 60/40 Balanced Allocation ETF</t>
-  </si>
-  <si>
-    <t>DFIV</t>
-  </si>
-  <si>
-    <t>Dimensional International Value ETF</t>
-  </si>
-  <si>
-    <t>IWD</t>
-  </si>
-  <si>
-    <t>iShares Russell 1000 Value ETF</t>
-  </si>
-  <si>
-    <t>AVGE</t>
-  </si>
-  <si>
-    <t>Avantis All Equity Markets ETF</t>
-  </si>
-  <si>
-    <t>HSCZ</t>
-  </si>
-  <si>
-    <t>iShares Currency Hedged MSCI EAFE Small-Cap ETF</t>
-  </si>
-  <si>
-    <t>FIDU</t>
-  </si>
-  <si>
-    <t>Fidelity MSCI Industrials Index ETF</t>
-  </si>
-  <si>
-    <t>FFLC</t>
-  </si>
-  <si>
-    <t>Fidelity Fundamental Large Cap Core ETF</t>
-  </si>
-  <si>
-    <t>RWR</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® Dow Jones® REIT ETF</t>
-  </si>
-  <si>
-    <t>PRN</t>
-  </si>
-  <si>
-    <t>Invesco Dorsey Wright Industrials Momentum ETF</t>
-  </si>
-  <si>
-    <t>USRT</t>
-  </si>
-  <si>
-    <t>iShares Core U.S. REIT ETF</t>
-  </si>
-  <si>
-    <t>KOKU</t>
-  </si>
-  <si>
-    <t>Xtrackers MSCI Kokusai Equity ETF</t>
-  </si>
-  <si>
-    <t>DFSV</t>
-  </si>
-  <si>
-    <t>Dimensional US Small Cap Value ETF</t>
-  </si>
-  <si>
-    <t>AVGV</t>
-  </si>
-  <si>
-    <t>Avantis ALL Equity Markets Value ETF</t>
-  </si>
-  <si>
-    <t>WELD</t>
-  </si>
-  <si>
-    <t>Tema U.S. Manufacturing &amp; Reshoring ETF</t>
-  </si>
-  <si>
-    <t>XSMO</t>
-  </si>
-  <si>
-    <t>Invesco S&amp;P SmallCap Momentum ETF</t>
-  </si>
-  <si>
-    <t>VIS</t>
-  </si>
-  <si>
-    <t>Vanguard Industrials Index Fund ETF Shares</t>
-  </si>
-  <si>
-    <t>SDCI</t>
-  </si>
-  <si>
-    <t>USCF SummerHaven Dynamic Commodity Strategy No K-1 Fund</t>
-  </si>
-  <si>
-    <t>BBRE</t>
-  </si>
-  <si>
-    <t>JPMorgan BetaBuilders MSCI U.S. REIT ETF</t>
-  </si>
-  <si>
-    <t>AVMA</t>
-  </si>
-  <si>
-    <t>Avantis Moderate Allocation ETF</t>
-  </si>
-  <si>
-    <t>AVUV</t>
-  </si>
-  <si>
-    <t>Avantis US Small Cap Value ETF</t>
-  </si>
-  <si>
-    <t>SAMT</t>
-  </si>
-  <si>
-    <t>Strategas Macro Thematic Opportunities ETF</t>
-  </si>
-  <si>
-    <t>MOOD</t>
-  </si>
-  <si>
-    <t>Relative Sentiment Tactical Allocation ETF</t>
-  </si>
-  <si>
-    <t>PVAL</t>
-  </si>
-  <si>
-    <t>Putnam Focused Large Cap Value ETF</t>
-  </si>
-  <si>
-    <t>IFRA</t>
-  </si>
-  <si>
-    <t>iShares U.S. Infrastructure ETF</t>
-  </si>
-  <si>
-    <t>EWI</t>
-  </si>
-  <si>
-    <t>iShares MSCI Italy ETF</t>
-  </si>
-  <si>
-    <t>XTL</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® S&amp;P® Telecom ETF</t>
-  </si>
-  <si>
-    <t>FEBT</t>
-  </si>
-  <si>
-    <t>Allianzim U.S. Equity Buffer10 Feb ETF</t>
-  </si>
-  <si>
-    <t>BUFR</t>
-  </si>
-  <si>
-    <t>FT Vest Laddered Buffer ETF</t>
-  </si>
-  <si>
-    <t>GVAL</t>
-  </si>
-  <si>
-    <t>Cambria Global Value ETF</t>
-  </si>
-  <si>
-    <t>XMVM</t>
-  </si>
-  <si>
-    <t>Invesco S&amp;P MidCap Value with Momentum ETF</t>
-  </si>
-  <si>
-    <t>SDVY</t>
-  </si>
-  <si>
-    <t>First Trust SMID Cap Rising Dividend Achievers ETF</t>
-  </si>
-  <si>
-    <t>HEZU</t>
-  </si>
-  <si>
-    <t>iShares Currency Hedged MSCI Eurozone ETF</t>
-  </si>
-  <si>
-    <t>VDC</t>
-  </si>
-  <si>
-    <t>Vanguard Consumer Staples Index Fund ETF Shares</t>
-  </si>
-  <si>
-    <t>BUFB</t>
-  </si>
-  <si>
-    <t>Innovator Laddered Allocation Buffer ETF</t>
-  </si>
-  <si>
-    <t>USVM</t>
-  </si>
-  <si>
-    <t>VictoryShares US Small Mid Cap Value Momentum ETF</t>
-  </si>
-  <si>
-    <t>USCI</t>
-  </si>
-  <si>
-    <t>United States Commodity Index Fund, LP</t>
-  </si>
-  <si>
-    <t>SPVM</t>
-  </si>
-  <si>
-    <t>Invesco S&amp;P 500 Value with Momentum ETF</t>
-  </si>
-  <si>
-    <t>PJFV</t>
-  </si>
-  <si>
-    <t>PGIM Jennison Focused Value ETF</t>
-  </si>
-  <si>
-    <t>MART</t>
-  </si>
-  <si>
-    <t>Allianzim U.S. Equity Buffer10 Mar ETF</t>
-  </si>
-  <si>
-    <t>IXG</t>
-  </si>
-  <si>
-    <t>iShares Global Financials ETF</t>
-  </si>
-  <si>
-    <t>KCE</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® S&amp;P® Capital Markets ETF</t>
-  </si>
-  <si>
-    <t>VNAM</t>
-  </si>
-  <si>
-    <t>Global X MSCI Vietnam ETF</t>
-  </si>
-  <si>
-    <t>PIT</t>
-  </si>
-  <si>
-    <t>VanEck Commodity Strategy ETF</t>
-  </si>
-  <si>
-    <t>ENFR</t>
-  </si>
-  <si>
-    <t>Alerian Energy Infrastructure ETF</t>
   </si>
 </sst>
 </file>
@@ -1260,43 +1260,43 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>78.02</v>
+        <v>43.22</v>
       </c>
       <c r="E2">
-        <v>7.7922</v>
+        <v>0.5729</v>
       </c>
       <c r="F2">
-        <v>5.64</v>
+        <v>0.2462</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>-0.1850994909763959</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>-0.0799999999999983</v>
       </c>
       <c r="I2">
-        <v>13.38706</v>
+        <v>3.67996</v>
       </c>
       <c r="J2">
-        <v>7.5796</v>
+        <v>9.56307</v>
       </c>
       <c r="K2">
-        <v>5.63368</v>
+        <v>11.86269</v>
       </c>
       <c r="L2">
-        <v>-2.46597</v>
+        <v>16.2836</v>
       </c>
       <c r="M2">
-        <v>-7.74192</v>
+        <v>16.52985</v>
       </c>
       <c r="N2">
-        <v>20.85886</v>
+        <v>26.60867</v>
       </c>
       <c r="O2">
-        <v>-1.51676</v>
+        <v>20.816</v>
       </c>
       <c r="P2">
-        <v>52.50172</v>
+        <v>38.11372</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -1310,13 +1310,13 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>44.91</v>
+        <v>75.33</v>
       </c>
       <c r="E3">
-        <v>3.9583</v>
+        <v>3.2484</v>
       </c>
       <c r="F3">
-        <v>1.71</v>
+        <v>2.37</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1325,28 +1325,28 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>14.34284</v>
+        <v>-0.54245</v>
       </c>
       <c r="J3">
-        <v>-0.80944</v>
+        <v>9.23444</v>
       </c>
       <c r="K3">
-        <v>-7.8031</v>
+        <v>1.97442</v>
       </c>
       <c r="L3">
-        <v>-20.66223</v>
+        <v>-1.18566</v>
       </c>
       <c r="M3">
-        <v>-13.82359</v>
+        <v>26.68855</v>
       </c>
       <c r="N3">
-        <v>-10.05861</v>
+        <v>43.16909</v>
       </c>
       <c r="O3">
-        <v>0.14009</v>
+        <v>38.7701</v>
       </c>
       <c r="P3">
-        <v>11.86195</v>
+        <v>55.16013</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -1360,43 +1360,43 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>256.04</v>
+        <v>102.723</v>
       </c>
       <c r="E4">
-        <v>3.5007</v>
+        <v>2.8311</v>
       </c>
       <c r="F4">
-        <v>8.66</v>
+        <v>2.8281</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>-0.5399959113343622</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>-0.5546999999999969</v>
       </c>
       <c r="I4">
-        <v>-0.59514</v>
+        <v>-0.79047</v>
       </c>
       <c r="J4">
-        <v>-2.51479</v>
+        <v>6.40625</v>
       </c>
       <c r="K4">
-        <v>11.69606</v>
+        <v>3.66416</v>
       </c>
       <c r="L4">
-        <v>19.29917</v>
+        <v>2.07596</v>
       </c>
       <c r="M4">
-        <v>19.51114</v>
+        <v>23.65271</v>
       </c>
       <c r="N4">
-        <v>26.95506</v>
+        <v>28.82143</v>
       </c>
       <c r="O4">
-        <v>20.86935</v>
+        <v>29.57285</v>
       </c>
       <c r="P4">
-        <v>51.15093</v>
+        <v>36.20837</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -1410,43 +1410,43 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>99.33</v>
+        <v>29.2899</v>
       </c>
       <c r="E5">
-        <v>3.1428</v>
+        <v>2.5916</v>
       </c>
       <c r="F5">
-        <v>3.0266</v>
+        <v>0.7399</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>-0.4639808808467035</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>-0.13589999999999947</v>
       </c>
       <c r="I5">
-        <v>-2.03933</v>
+        <v>-0.78233</v>
       </c>
       <c r="J5">
-        <v>2.59344</v>
+        <v>6.42359</v>
       </c>
       <c r="K5">
-        <v>6.3121</v>
+        <v>3.75385</v>
       </c>
       <c r="L5">
-        <v>3.49566</v>
+        <v>2.18182</v>
       </c>
       <c r="M5">
-        <v>1.05184</v>
+        <v>23.84738</v>
       </c>
       <c r="N5">
-        <v>-15.82147</v>
+        <v>29.10921</v>
       </c>
       <c r="O5">
-        <v>-9.3142</v>
+        <v>29.88626</v>
       </c>
       <c r="P5">
-        <v>-13.08895</v>
+        <v>36.68534</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -1460,43 +1460,43 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>67.36</v>
+        <v>33.17</v>
       </c>
       <c r="E6">
-        <v>2.9183</v>
+        <v>1.5926</v>
       </c>
       <c r="F6">
-        <v>1.91</v>
+        <v>0.52</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.045085662759222905</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.014999999999993463</v>
       </c>
       <c r="I6">
-        <v>9.48545</v>
+        <v>1.77884</v>
       </c>
       <c r="J6">
-        <v>5.28494</v>
+        <v>7.72936</v>
       </c>
       <c r="K6">
-        <v>0.87905</v>
+        <v>5.87408</v>
       </c>
       <c r="L6">
-        <v>-2.16996</v>
+        <v>1.38737</v>
       </c>
       <c r="M6">
-        <v>-2.82889</v>
+        <v>21.50341</v>
       </c>
       <c r="N6">
-        <v>15.0102</v>
+        <v>32.40255</v>
       </c>
       <c r="O6">
-        <v>6.66212</v>
+        <v>31.92741</v>
       </c>
       <c r="P6">
-        <v>41.49154</v>
+        <v>43.37945</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -1510,43 +1510,43 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>64.6276</v>
+        <v>157.37</v>
       </c>
       <c r="E7">
-        <v>2.6412</v>
+        <v>1.8642</v>
       </c>
       <c r="F7">
-        <v>1.663</v>
+        <v>2.88</v>
       </c>
       <c r="G7">
-        <v>-0.0006189267809603698</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>-0.00039999999999906777</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>2.62945</v>
+        <v>2.73016</v>
       </c>
       <c r="J7">
-        <v>4.71574</v>
+        <v>3.39388</v>
       </c>
       <c r="K7">
-        <v>6.63176</v>
+        <v>6.12132</v>
       </c>
       <c r="L7">
-        <v>5.93527</v>
+        <v>9.1737</v>
       </c>
       <c r="M7">
-        <v>10.90258</v>
+        <v>13.60701</v>
       </c>
       <c r="N7">
-        <v>20.95157</v>
+        <v>24.661</v>
       </c>
       <c r="O7">
-        <v>14.24851</v>
+        <v>22.38725</v>
       </c>
       <c r="P7">
-        <v>22.98897</v>
+        <v>28.39408</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -1560,43 +1560,43 @@
         <v>1</v>
       </c>
       <c r="D8">
-        <v>97.2</v>
+        <v>52.27</v>
       </c>
       <c r="E8">
-        <v>2.5316</v>
+        <v>1.6037</v>
       </c>
       <c r="F8">
-        <v>2.4</v>
+        <v>0.825</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.03826286588864745</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.01999999999999602</v>
       </c>
       <c r="I8">
-        <v>6.61046</v>
+        <v>3.56746</v>
       </c>
       <c r="J8">
-        <v>-6.58063</v>
+        <v>8.53462</v>
       </c>
       <c r="K8">
-        <v>-1.38865</v>
+        <v>12.04493</v>
       </c>
       <c r="L8">
-        <v>5.08715</v>
+        <v>19.83959</v>
       </c>
       <c r="M8">
-        <v>49.94185</v>
+        <v>27.84196</v>
       </c>
       <c r="N8">
-        <v>72.14135</v>
+        <v>37.03344</v>
       </c>
       <c r="O8">
-        <v>70.40925</v>
+        <v>31.31734</v>
       </c>
       <c r="P8">
-        <v>117.91254</v>
+        <v>51.57703</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -1610,13 +1610,13 @@
         <v>1</v>
       </c>
       <c r="D9">
-        <v>46.27</v>
+        <v>101.89</v>
       </c>
       <c r="E9">
-        <v>2.4126</v>
+        <v>1.5549</v>
       </c>
       <c r="F9">
-        <v>1.09</v>
+        <v>1.56</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1625,28 +1625,28 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>4.09289</v>
+        <v>1.93229</v>
       </c>
       <c r="J9">
-        <v>-0.33025</v>
+        <v>3.02451</v>
       </c>
       <c r="K9">
-        <v>3.68484</v>
+        <v>7.80274</v>
       </c>
       <c r="L9">
-        <v>10.1415</v>
+        <v>10.18631</v>
       </c>
       <c r="M9">
-        <v>22.19753</v>
+        <v>16.2708</v>
       </c>
       <c r="N9">
-        <v>24.45791</v>
+        <v>26.90056</v>
       </c>
       <c r="O9">
-        <v>23.15998</v>
+        <v>22.97956</v>
       </c>
       <c r="P9">
-        <v>36.27466</v>
+        <v>35.95284</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1660,43 +1660,43 @@
         <v>1</v>
       </c>
       <c r="D10">
-        <v>57.86</v>
+        <v>120.84</v>
       </c>
       <c r="E10">
-        <v>2.3339</v>
+        <v>0.8134</v>
       </c>
       <c r="F10">
-        <v>1.3196</v>
+        <v>0.975</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.008276090374911128</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>0.010000000000005116</v>
       </c>
       <c r="I10">
-        <v>5.14035</v>
+        <v>8.8116</v>
       </c>
       <c r="J10">
-        <v>1.86049</v>
+        <v>4.19321</v>
       </c>
       <c r="K10">
-        <v>-3.65643</v>
+        <v>1.00182</v>
       </c>
       <c r="L10">
-        <v>-8.12381</v>
+        <v>9.87296</v>
       </c>
       <c r="M10">
-        <v>-13.28164</v>
+        <v>20.51483</v>
       </c>
       <c r="N10">
-        <v>5.89164</v>
+        <v>54.42738</v>
       </c>
       <c r="O10">
-        <v>-2.43841</v>
+        <v>41.34461</v>
       </c>
       <c r="P10">
-        <v>24.44735</v>
+        <v>73.98144</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -1710,43 +1710,43 @@
         <v>1</v>
       </c>
       <c r="D11">
-        <v>42.78</v>
+        <v>40.8599</v>
       </c>
       <c r="E11">
-        <v>2.2956</v>
+        <v>0.7891</v>
       </c>
       <c r="F11">
-        <v>0.96</v>
+        <v>0.3199</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>-0.08812729498164348</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>-0.036000000000001364</v>
       </c>
       <c r="I11">
-        <v>3.81032</v>
+        <v>2.77142</v>
       </c>
       <c r="J11">
-        <v>3.04896</v>
+        <v>2.98089</v>
       </c>
       <c r="K11">
-        <v>-2.25909</v>
+        <v>0.02475</v>
       </c>
       <c r="L11">
-        <v>-9.3692</v>
+        <v>-3.60124</v>
       </c>
       <c r="M11">
-        <v>-13.82359</v>
+        <v>3.08595</v>
       </c>
       <c r="N11">
-        <v>6.91726</v>
+        <v>20.0589</v>
       </c>
       <c r="O11">
-        <v>-1.03416</v>
+        <v>15.84981</v>
       </c>
       <c r="P11">
-        <v>26.34887</v>
+        <v>29.57485</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1760,43 +1760,43 @@
         <v>1</v>
       </c>
       <c r="D12">
-        <v>85.95</v>
+        <v>54.61</v>
       </c>
       <c r="E12">
-        <v>2.2849</v>
+        <v>0.6636</v>
       </c>
       <c r="F12">
-        <v>1.92</v>
+        <v>0.36</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>0.036636746656889575</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>0.01999999999999602</v>
       </c>
       <c r="I12">
-        <v>5.14112</v>
+        <v>1.53287</v>
       </c>
       <c r="J12">
-        <v>1.86521</v>
+        <v>4.81902</v>
       </c>
       <c r="K12">
-        <v>-3.64821</v>
+        <v>7.38891</v>
       </c>
       <c r="L12">
-        <v>-8.11186</v>
+        <v>10.12154</v>
       </c>
       <c r="M12">
-        <v>-13.2599</v>
+        <v>11.08253</v>
       </c>
       <c r="N12">
-        <v>5.92978</v>
+        <v>25.34359</v>
       </c>
       <c r="O12">
-        <v>-2.41</v>
+        <v>19.35279</v>
       </c>
       <c r="P12">
-        <v>24.50734</v>
+        <v>35.99488</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1810,13 +1810,13 @@
         <v>1</v>
       </c>
       <c r="D13">
-        <v>43.29</v>
+        <v>38.83</v>
       </c>
       <c r="E13">
-        <v>2.2679</v>
+        <v>0.6219</v>
       </c>
       <c r="F13">
-        <v>0.96</v>
+        <v>0.24</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1825,28 +1825,28 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>5.14133</v>
+        <v>-2.58458</v>
       </c>
       <c r="J13">
-        <v>1.86778</v>
+        <v>-1.23146</v>
       </c>
       <c r="K13">
-        <v>-3.64367</v>
+        <v>0.00026</v>
       </c>
       <c r="L13">
-        <v>-8.10523</v>
+        <v>2.49189</v>
       </c>
       <c r="M13">
-        <v>-13.24724</v>
+        <v>13.56774</v>
       </c>
       <c r="N13">
-        <v>5.95222</v>
+        <v>29.38191</v>
       </c>
       <c r="O13">
-        <v>-2.39353</v>
+        <v>25.15697</v>
       </c>
       <c r="P13">
-        <v>24.54233</v>
+        <v>26.27112</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1860,43 +1860,43 @@
         <v>1</v>
       </c>
       <c r="D14">
-        <v>51.46</v>
+        <v>257.4</v>
       </c>
       <c r="E14">
-        <v>2.2249</v>
+        <v>0.5312</v>
       </c>
       <c r="F14">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>0.027202424901874318</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>0.06999999999999318</v>
       </c>
       <c r="I14">
-        <v>0.39841</v>
+        <v>4.45034</v>
       </c>
       <c r="J14">
-        <v>7.29059</v>
+        <v>-0.10533</v>
       </c>
       <c r="K14">
-        <v>9.68713</v>
+        <v>14.92303</v>
       </c>
       <c r="L14">
-        <v>17.26327</v>
+        <v>21.22905</v>
       </c>
       <c r="M14">
-        <v>28.45607</v>
+        <v>20.34026</v>
       </c>
       <c r="N14">
-        <v>34.80796</v>
+        <v>31.52866</v>
       </c>
       <c r="O14">
-        <v>28.55398</v>
+        <v>24.36134</v>
       </c>
       <c r="P14">
-        <v>46.95704</v>
+        <v>56.09607</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -1910,43 +1910,43 @@
         <v>1</v>
       </c>
       <c r="D15">
-        <v>42.81</v>
+        <v>189.23</v>
       </c>
       <c r="E15">
-        <v>2.1962</v>
+        <v>0.5206</v>
       </c>
       <c r="F15">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>0.12169312169311627</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>0.22999999999998977</v>
       </c>
       <c r="I15">
-        <v>3.79965</v>
+        <v>1.13236</v>
       </c>
       <c r="J15">
-        <v>3.03698</v>
+        <v>-0.2553</v>
       </c>
       <c r="K15">
-        <v>-2.25372</v>
+        <v>4.94591</v>
       </c>
       <c r="L15">
-        <v>-9.37096</v>
+        <v>6.90377</v>
       </c>
       <c r="M15">
-        <v>-13.8263</v>
+        <v>6.16314</v>
       </c>
       <c r="N15">
-        <v>6.91233</v>
+        <v>8.87484</v>
       </c>
       <c r="O15">
-        <v>-1.03505</v>
+        <v>5.69271</v>
       </c>
       <c r="P15">
-        <v>26.33634</v>
+        <v>9.86273</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -1960,13 +1960,13 @@
         <v>1</v>
       </c>
       <c r="D16">
-        <v>582.7</v>
+        <v>83.84</v>
       </c>
       <c r="E16">
-        <v>1.9633</v>
+        <v>0.4673</v>
       </c>
       <c r="F16">
-        <v>11.22</v>
+        <v>0.39</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1975,28 +1975,28 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>13.26636</v>
+        <v>5.03673</v>
       </c>
       <c r="J16">
-        <v>-3.67406</v>
+        <v>4.16527</v>
       </c>
       <c r="K16">
-        <v>0.08948</v>
+        <v>6.21564</v>
       </c>
       <c r="L16">
-        <v>9.06762</v>
+        <v>9.79837</v>
       </c>
       <c r="M16">
-        <v>49.58049</v>
+        <v>22.25693</v>
       </c>
       <c r="N16">
-        <v>59.10907</v>
+        <v>25.06685</v>
       </c>
       <c r="O16">
-        <v>58.42381</v>
+        <v>22.73103</v>
       </c>
       <c r="P16">
-        <v>99.34915</v>
+        <v>36.7907</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -2010,43 +2010,43 @@
         <v>1</v>
       </c>
       <c r="D17">
-        <v>117.38</v>
+        <v>135.2885</v>
       </c>
       <c r="E17">
-        <v>1.9366</v>
+        <v>0.4609</v>
       </c>
       <c r="F17">
-        <v>2.23</v>
+        <v>0.6207</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>-0.0003695791971174128</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>-0.0004999999999881766</v>
       </c>
       <c r="I17">
-        <v>2.90466</v>
+        <v>3.36448</v>
       </c>
       <c r="J17">
-        <v>-0.59149</v>
+        <v>3.53284</v>
       </c>
       <c r="K17">
-        <v>2.56709</v>
+        <v>5.55362</v>
       </c>
       <c r="L17">
-        <v>1.65091</v>
+        <v>6.0694</v>
       </c>
       <c r="M17">
-        <v>10.36702</v>
+        <v>11.55353</v>
       </c>
       <c r="N17">
-        <v>21.96711</v>
+        <v>16.85335</v>
       </c>
       <c r="O17">
-        <v>19.12745</v>
+        <v>13.7088</v>
       </c>
       <c r="P17">
-        <v>25.04161</v>
+        <v>23.52698</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -2060,43 +2060,43 @@
         <v>1</v>
       </c>
       <c r="D18">
-        <v>157.37</v>
+        <v>77.655</v>
       </c>
       <c r="E18">
-        <v>1.8642</v>
+        <v>0.3946</v>
       </c>
       <c r="F18">
-        <v>2.88</v>
+        <v>0.3052</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>0.28401755744902285</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>0.22000000000001307</v>
       </c>
       <c r="I18">
-        <v>2.1274</v>
+        <v>0.27202</v>
       </c>
       <c r="J18">
-        <v>2.28944</v>
+        <v>2.13749</v>
       </c>
       <c r="K18">
-        <v>5.32161</v>
+        <v>5.78308</v>
       </c>
       <c r="L18">
-        <v>8.33827</v>
+        <v>10.25131</v>
       </c>
       <c r="M18">
-        <v>15.51121</v>
+        <v>8.10066</v>
       </c>
       <c r="N18">
-        <v>24.00691</v>
+        <v>20.17355</v>
       </c>
       <c r="O18">
-        <v>21.46496</v>
+        <v>15.49257</v>
       </c>
       <c r="P18">
-        <v>27.01789</v>
+        <v>29.09685</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -2110,13 +2110,13 @@
         <v>1</v>
       </c>
       <c r="D19">
-        <v>157.37</v>
+        <v>44.2</v>
       </c>
       <c r="E19">
-        <v>1.8576</v>
+        <v>0.4205</v>
       </c>
       <c r="F19">
-        <v>2.87</v>
+        <v>0.1851</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2125,28 +2125,28 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>3.42326</v>
+        <v>1.17992</v>
       </c>
       <c r="J19">
-        <v>-4.64437</v>
+        <v>0.98002</v>
       </c>
       <c r="K19">
-        <v>18.99757</v>
+        <v>2.22557</v>
       </c>
       <c r="L19">
-        <v>14.50633</v>
+        <v>2.20657</v>
       </c>
       <c r="M19">
-        <v>26.87834</v>
+        <v>6.09325</v>
       </c>
       <c r="N19">
-        <v>40.65931</v>
+        <v>20.6424</v>
       </c>
       <c r="O19">
-        <v>25.61071</v>
+        <v>14.64664</v>
       </c>
       <c r="P19">
-        <v>77.05707</v>
+        <v>30.94392</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -2160,43 +2160,43 @@
         <v>1</v>
       </c>
       <c r="D20">
-        <v>42.9738</v>
+        <v>64.7901</v>
       </c>
       <c r="E20">
-        <v>1.8257</v>
+        <v>0.1204</v>
       </c>
       <c r="F20">
-        <v>0.7705</v>
+        <v>0.0779</v>
       </c>
       <c r="G20">
-        <v>-0.0004653976823184575</v>
+        <v>0.18501387604071007</v>
       </c>
       <c r="H20">
-        <v>-0.00019999999999953388</v>
+        <v>0.12000000000000455</v>
       </c>
       <c r="I20">
-        <v>0.08836</v>
+        <v>3.97518</v>
       </c>
       <c r="J20">
-        <v>8.82939</v>
+        <v>1.48386</v>
       </c>
       <c r="K20">
-        <v>10.35384</v>
+        <v>6.07797</v>
       </c>
       <c r="L20">
-        <v>14.34567</v>
+        <v>8.17175</v>
       </c>
       <c r="M20">
-        <v>17.67484</v>
+        <v>11.03254</v>
       </c>
       <c r="N20">
-        <v>25.81288</v>
+        <v>27.76662</v>
       </c>
       <c r="O20">
-        <v>19.18639</v>
+        <v>23.64487</v>
       </c>
       <c r="P20">
-        <v>35.27272</v>
+        <v>45.94827</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -2210,13 +2210,13 @@
         <v>1</v>
       </c>
       <c r="D21">
-        <v>289.84</v>
+        <v>99.717</v>
       </c>
       <c r="E21">
-        <v>1.5379</v>
+        <v>0.3896</v>
       </c>
       <c r="F21">
-        <v>4.39</v>
+        <v>0.387</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2225,28 +2225,28 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>5.31041</v>
+        <v>4.67329</v>
       </c>
       <c r="J21">
-        <v>2.71919</v>
+        <v>6.44017</v>
       </c>
       <c r="K21">
-        <v>3.79574</v>
+        <v>11.78862</v>
       </c>
       <c r="L21">
-        <v>9.28644</v>
+        <v>9.25946</v>
       </c>
       <c r="M21">
-        <v>29.5917</v>
+        <v>4.34233</v>
       </c>
       <c r="N21">
-        <v>26.05572</v>
+        <v>-10.50506</v>
       </c>
       <c r="O21">
-        <v>27.33834</v>
+        <v>-4.64265</v>
       </c>
       <c r="P21">
-        <v>39.32412</v>
+        <v>-10.60883</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -2260,13 +2260,13 @@
         <v>1</v>
       </c>
       <c r="D22">
-        <v>99.13</v>
+        <v>106.19</v>
       </c>
       <c r="E22">
-        <v>1.5156</v>
+        <v>0.3781</v>
       </c>
       <c r="F22">
-        <v>1.48</v>
+        <v>0.4</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -2275,28 +2275,28 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>4.51043</v>
+        <v>3.32412</v>
       </c>
       <c r="J22">
-        <v>1.10507</v>
+        <v>4.90431</v>
       </c>
       <c r="K22">
-        <v>6.49319</v>
+        <v>6.43841</v>
       </c>
       <c r="L22">
-        <v>9.93081</v>
+        <v>7.13454</v>
       </c>
       <c r="M22">
-        <v>22.91098</v>
+        <v>12.52222</v>
       </c>
       <c r="N22">
-        <v>21.41427</v>
+        <v>24.49303</v>
       </c>
       <c r="O22">
-        <v>23.4122</v>
+        <v>14.67454</v>
       </c>
       <c r="P22">
-        <v>22.23353</v>
+        <v>30.49729</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -2310,13 +2310,13 @@
         <v>1</v>
       </c>
       <c r="D23">
-        <v>90.74</v>
+        <v>24.1</v>
       </c>
       <c r="E23">
-        <v>1.4535</v>
+        <v>0.3539</v>
       </c>
       <c r="F23">
-        <v>1.3</v>
+        <v>0.085</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -2325,28 +2325,28 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>6.34457</v>
+        <v>2.1322</v>
       </c>
       <c r="J23">
-        <v>6.08884</v>
+        <v>-4.50558</v>
       </c>
       <c r="K23">
-        <v>15.29704</v>
+        <v>-4.05806</v>
       </c>
       <c r="L23">
-        <v>15.5696</v>
+        <v>-9.07891</v>
       </c>
       <c r="M23">
-        <v>7.03847</v>
+        <v>1.50674</v>
       </c>
       <c r="N23">
-        <v>48.68485</v>
+        <v>9.99938</v>
       </c>
       <c r="O23">
-        <v>27.23023</v>
+        <v>-3.20593</v>
       </c>
       <c r="P23">
-        <v>82.802</v>
+        <v>13.36724</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -2360,43 +2360,43 @@
         <v>1</v>
       </c>
       <c r="D24">
-        <v>85.037</v>
+        <v>194.13</v>
       </c>
       <c r="E24">
-        <v>1.4306</v>
+        <v>-0.0309</v>
       </c>
       <c r="F24">
-        <v>1.1994</v>
+        <v>-0.06</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>0.3682624707063961</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>0.7150000000000034</v>
       </c>
       <c r="I24">
-        <v>16.83303</v>
+        <v>5.09217</v>
       </c>
       <c r="J24">
-        <v>-8.54592</v>
+        <v>4.39576</v>
       </c>
       <c r="K24">
-        <v>-3.62131</v>
+        <v>5.68186</v>
       </c>
       <c r="L24">
-        <v>10.05287</v>
+        <v>6.05013</v>
       </c>
       <c r="M24">
-        <v>58.25638</v>
+        <v>17.25341</v>
       </c>
       <c r="N24">
-        <v>83.4547</v>
+        <v>17.70897</v>
       </c>
       <c r="O24">
-        <v>79.84521</v>
+        <v>15.95725</v>
       </c>
       <c r="P24">
-        <v>150.10034</v>
+        <v>25.64757</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -2410,13 +2410,13 @@
         <v>1</v>
       </c>
       <c r="D25">
-        <v>120.005</v>
+        <v>42.95</v>
       </c>
       <c r="E25">
-        <v>1.4155</v>
+        <v>0.327</v>
       </c>
       <c r="F25">
-        <v>1.675</v>
+        <v>0.14</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -2425,28 +2425,28 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>10.73258</v>
+        <v>7.65743</v>
       </c>
       <c r="J25">
-        <v>-1.6239</v>
+        <v>4.32023</v>
       </c>
       <c r="K25">
-        <v>-1.62718</v>
+        <v>-0.69703</v>
       </c>
       <c r="L25">
-        <v>6.12428</v>
+        <v>-8.63617</v>
       </c>
       <c r="M25">
-        <v>23.31705</v>
+        <v>-12.45391</v>
       </c>
       <c r="N25">
-        <v>48.45761</v>
+        <v>8.39462</v>
       </c>
       <c r="O25">
-        <v>37.6655</v>
+        <v>0.54105</v>
       </c>
       <c r="P25">
-        <v>69.55189</v>
+        <v>27.88749</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -2460,13 +2460,13 @@
         <v>1</v>
       </c>
       <c r="D26">
-        <v>89.87</v>
+        <v>23.255</v>
       </c>
       <c r="E26">
-        <v>1.4105</v>
+        <v>0.3236</v>
       </c>
       <c r="F26">
-        <v>1.25</v>
+        <v>0.075</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -2475,28 +2475,28 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>4.44995</v>
+        <v>4.43172</v>
       </c>
       <c r="J26">
-        <v>1.1028</v>
+        <v>0.71304</v>
       </c>
       <c r="K26">
-        <v>6.21234</v>
+        <v>3.3738</v>
       </c>
       <c r="L26">
-        <v>7.22173</v>
+        <v>5.65108</v>
       </c>
       <c r="M26">
-        <v>16.18792</v>
+        <v>12.55041</v>
       </c>
       <c r="N26">
-        <v>21.15144</v>
+        <v>7.47496</v>
       </c>
       <c r="O26">
-        <v>19.76238</v>
+        <v>10.2103</v>
       </c>
       <c r="P26">
-        <v>29.81146</v>
+        <v>13.96588</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -2510,43 +2510,43 @@
         <v>1</v>
       </c>
       <c r="D27">
-        <v>23.18</v>
+        <v>43.42</v>
       </c>
       <c r="E27">
-        <v>1.3918</v>
+        <v>0.3235</v>
       </c>
       <c r="F27">
-        <v>0.3182</v>
+        <v>0.14</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>0.02303616678185929</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>0.010000000000005116</v>
       </c>
       <c r="I27">
-        <v>9.55702</v>
+        <v>7.67137</v>
       </c>
       <c r="J27">
-        <v>-0.55182</v>
+        <v>4.31908</v>
       </c>
       <c r="K27">
-        <v>3.74866</v>
+        <v>-0.69028</v>
       </c>
       <c r="L27">
-        <v>6.68625</v>
+        <v>-8.61382</v>
       </c>
       <c r="M27">
-        <v>16.93577</v>
+        <v>-12.40865</v>
       </c>
       <c r="N27">
-        <v>5.72532</v>
+        <v>8.49202</v>
       </c>
       <c r="O27">
-        <v>10.60995</v>
+        <v>0.59817</v>
       </c>
       <c r="P27">
-        <v>15.76037</v>
+        <v>28.03957</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -2560,43 +2560,43 @@
         <v>1</v>
       </c>
       <c r="D28">
-        <v>254.05</v>
+        <v>258.35</v>
       </c>
       <c r="E28">
-        <v>1.3807</v>
+        <v>0.3067</v>
       </c>
       <c r="F28">
-        <v>3.46</v>
+        <v>0.79</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>0.02710236952146896</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>0.07000000000005002</v>
       </c>
       <c r="I28">
-        <v>10.60977</v>
+        <v>2.32583</v>
       </c>
       <c r="J28">
-        <v>3.17551</v>
+        <v>3.99542</v>
       </c>
       <c r="K28">
-        <v>4.26523</v>
+        <v>9.33491</v>
       </c>
       <c r="L28">
-        <v>11.63264</v>
+        <v>11.38826</v>
       </c>
       <c r="M28">
-        <v>34.66016</v>
+        <v>15.46241</v>
       </c>
       <c r="N28">
-        <v>23.16796</v>
+        <v>27.49164</v>
       </c>
       <c r="O28">
-        <v>26.00131</v>
+        <v>23.35414</v>
       </c>
       <c r="P28">
-        <v>40.01433</v>
+        <v>34.53576</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
@@ -2610,13 +2610,13 @@
         <v>1</v>
       </c>
       <c r="D29">
-        <v>45.59</v>
+        <v>67.5</v>
       </c>
       <c r="E29">
-        <v>1.3562</v>
+        <v>0.2972</v>
       </c>
       <c r="F29">
-        <v>0.61</v>
+        <v>0.2</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -2625,28 +2625,28 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>1.72453</v>
+        <v>2.24411</v>
       </c>
       <c r="J29">
-        <v>2.02549</v>
+        <v>4.90728</v>
       </c>
       <c r="K29">
-        <v>14.19658</v>
+        <v>10.39318</v>
       </c>
       <c r="L29">
-        <v>11.15884</v>
+        <v>17.19015</v>
       </c>
       <c r="M29">
-        <v>19.18184</v>
+        <v>19.78748</v>
       </c>
       <c r="N29">
-        <v>33.98217</v>
+        <v>32.76692</v>
       </c>
       <c r="O29">
-        <v>29.3257</v>
+        <v>28.15959</v>
       </c>
       <c r="P29">
-        <v>43.56496</v>
+        <v>38.29487</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -2660,43 +2660,43 @@
         <v>1</v>
       </c>
       <c r="D30">
-        <v>109.63</v>
+        <v>86.19</v>
       </c>
       <c r="E30">
-        <v>1.3404</v>
+        <v>0.2792</v>
       </c>
       <c r="F30">
-        <v>1.45</v>
+        <v>0.24</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>0.08707767328457315</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>0.07500000000000284</v>
       </c>
       <c r="I30">
-        <v>4.90583</v>
+        <v>7.67141</v>
       </c>
       <c r="J30">
-        <v>3.50125</v>
+        <v>4.31691</v>
       </c>
       <c r="K30">
-        <v>3.15257</v>
+        <v>-0.69488</v>
       </c>
       <c r="L30">
-        <v>2.64559</v>
+        <v>-8.62046</v>
       </c>
       <c r="M30">
-        <v>8.16619</v>
+        <v>-12.42142</v>
       </c>
       <c r="N30">
-        <v>25.61538</v>
+        <v>8.46924</v>
       </c>
       <c r="O30">
-        <v>16.47567</v>
+        <v>0.58128</v>
       </c>
       <c r="P30">
-        <v>36.21871</v>
+        <v>28.0039</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -2710,43 +2710,43 @@
         <v>1</v>
       </c>
       <c r="D31">
-        <v>105.08</v>
+        <v>45.71</v>
       </c>
       <c r="E31">
-        <v>1.3308</v>
+        <v>0.2852</v>
       </c>
       <c r="F31">
-        <v>1.38</v>
+        <v>0.13</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>-0.010937329104238341</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>-0.005000000000002558</v>
       </c>
       <c r="I31">
-        <v>7.85094</v>
+        <v>4.00549</v>
       </c>
       <c r="J31">
-        <v>2.10276</v>
+        <v>4.24409</v>
       </c>
       <c r="K31">
-        <v>2.67422</v>
+        <v>15.75045</v>
       </c>
       <c r="L31">
-        <v>4.32953</v>
+        <v>14.33286</v>
       </c>
       <c r="M31">
-        <v>17.4128</v>
+        <v>20.80354</v>
       </c>
       <c r="N31">
-        <v>12.84523</v>
+        <v>35.17121</v>
       </c>
       <c r="O31">
-        <v>13.96498</v>
+        <v>31.08543</v>
       </c>
       <c r="P31">
-        <v>26.95721</v>
+        <v>44.29978</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
@@ -2760,43 +2760,43 @@
         <v>1</v>
       </c>
       <c r="D32">
-        <v>42.29</v>
+        <v>164.0365</v>
       </c>
       <c r="E32">
-        <v>1.2692</v>
+        <v>0.2522</v>
       </c>
       <c r="F32">
-        <v>0.53</v>
+        <v>0.4126</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>-0.00030480928084310145</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>-0.0005000000000165983</v>
       </c>
       <c r="I32">
-        <v>2.72387</v>
+        <v>2.24528</v>
       </c>
       <c r="J32">
-        <v>3.99975</v>
+        <v>4.59204</v>
       </c>
       <c r="K32">
-        <v>7.19617</v>
+        <v>9.88251</v>
       </c>
       <c r="L32">
-        <v>8.61951</v>
+        <v>8.1993</v>
       </c>
       <c r="M32">
-        <v>15.55223</v>
+        <v>9.87548</v>
       </c>
       <c r="N32">
-        <v>18.83315</v>
+        <v>13.53949</v>
       </c>
       <c r="O32">
-        <v>16.22796</v>
+        <v>10.35404</v>
       </c>
       <c r="P32">
-        <v>22.0489</v>
+        <v>10.08385</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -2810,43 +2810,43 @@
         <v>1</v>
       </c>
       <c r="D33">
-        <v>132.43</v>
+        <v>49.9662</v>
       </c>
       <c r="E33">
-        <v>1.2462</v>
+        <v>-0.3268</v>
       </c>
       <c r="F33">
-        <v>1.63</v>
+        <v>-0.1638</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>0.40000000000000563</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>0.20000000000000284</v>
       </c>
       <c r="I33">
-        <v>6.43236</v>
+        <v>4.77158</v>
       </c>
       <c r="J33">
-        <v>-6.5746</v>
+        <v>2.5348</v>
       </c>
       <c r="K33">
-        <v>-4.20459</v>
+        <v>2.0517</v>
       </c>
       <c r="L33">
-        <v>-1.84794</v>
+        <v>1.52044</v>
       </c>
       <c r="M33">
-        <v>17.09169</v>
+        <v>9.53578</v>
       </c>
       <c r="N33">
-        <v>23.96114</v>
+        <v>8.13161</v>
       </c>
       <c r="O33">
-        <v>25.03736</v>
+        <v>7.06232</v>
       </c>
       <c r="P33">
-        <v>41.61354</v>
+        <v>16.65245</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -2860,13 +2860,13 @@
         <v>1</v>
       </c>
       <c r="D34">
-        <v>35.85</v>
+        <v>42.37</v>
       </c>
       <c r="E34">
-        <v>1.214</v>
+        <v>0.201</v>
       </c>
       <c r="F34">
-        <v>0.43</v>
+        <v>0.085</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -2875,28 +2875,28 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>5.6913</v>
+        <v>2.90854</v>
       </c>
       <c r="J34">
-        <v>2.10132</v>
+        <v>4.74467</v>
       </c>
       <c r="K34">
-        <v>2.85164</v>
+        <v>7.88171</v>
       </c>
       <c r="L34">
-        <v>5.33656</v>
+        <v>9.56047</v>
       </c>
       <c r="M34">
-        <v>9.29755</v>
+        <v>13.46432</v>
       </c>
       <c r="N34">
-        <v>25.24464</v>
+        <v>19.48064</v>
       </c>
       <c r="O34">
-        <v>17.7189</v>
+        <v>16.97126</v>
       </c>
       <c r="P34">
-        <v>35.4302</v>
+        <v>23.24191</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -2910,43 +2910,43 @@
         <v>1</v>
       </c>
       <c r="D35">
-        <v>79.6333</v>
+        <v>50.71</v>
       </c>
       <c r="E35">
-        <v>1.1988</v>
+        <v>0.1976</v>
       </c>
       <c r="F35">
-        <v>0.9433</v>
+        <v>0.1</v>
       </c>
       <c r="G35">
-        <v>0.0003767282408171976</v>
+        <v>0.07894217485691563</v>
       </c>
       <c r="H35">
-        <v>0.00030000000000995897</v>
+        <v>0.03999999999999915</v>
       </c>
       <c r="I35">
-        <v>4.46059</v>
+        <v>2.94895</v>
       </c>
       <c r="J35">
-        <v>3.18312</v>
+        <v>5.39246</v>
       </c>
       <c r="K35">
-        <v>3.85625</v>
+        <v>6.3473</v>
       </c>
       <c r="L35">
-        <v>3.05725</v>
+        <v>12.36518</v>
       </c>
       <c r="M35">
-        <v>7.05278</v>
+        <v>17.74894</v>
       </c>
       <c r="N35">
-        <v>21.13962</v>
+        <v>28.98734</v>
       </c>
       <c r="O35">
-        <v>13.72106</v>
+        <v>23.14375</v>
       </c>
       <c r="P35">
-        <v>26.91918</v>
+        <v>43.15001</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -2960,43 +2960,43 @@
         <v>1</v>
       </c>
       <c r="D36">
-        <v>45.9503</v>
+        <v>56.6</v>
       </c>
       <c r="E36">
-        <v>1.1849</v>
+        <v>0.1947</v>
       </c>
       <c r="F36">
-        <v>0.5381</v>
+        <v>0.11</v>
       </c>
       <c r="G36">
-        <v>0.000652883569087591</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>0.0002999999999957481</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>2.19793</v>
+        <v>2.97518</v>
       </c>
       <c r="J36">
-        <v>0.13944</v>
+        <v>0.63901</v>
       </c>
       <c r="K36">
-        <v>1.71442</v>
+        <v>5.46577</v>
       </c>
       <c r="L36">
-        <v>8.58585</v>
+        <v>8.90653</v>
       </c>
       <c r="M36">
-        <v>13.36391</v>
+        <v>6.60037</v>
       </c>
       <c r="N36">
-        <v>27.58743</v>
+        <v>27.93804</v>
       </c>
       <c r="O36">
-        <v>21.76506</v>
+        <v>21.63352</v>
       </c>
       <c r="P36">
-        <v>45.65149</v>
+        <v>35.71555</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -3010,43 +3010,43 @@
         <v>1</v>
       </c>
       <c r="D37">
-        <v>28.31</v>
+        <v>185.35</v>
       </c>
       <c r="E37">
-        <v>1.1794</v>
+        <v>0.1946</v>
       </c>
       <c r="F37">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>0.010791560999288732</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>0.01999999999998181</v>
       </c>
       <c r="I37">
-        <v>6.17237</v>
+        <v>1.71218</v>
       </c>
       <c r="J37">
-        <v>-1.22549</v>
+        <v>3.87383</v>
       </c>
       <c r="K37">
-        <v>-8.24856</v>
+        <v>8.04465</v>
       </c>
       <c r="L37">
-        <v>-3.33051</v>
+        <v>10.23444</v>
       </c>
       <c r="M37">
-        <v>20.64121</v>
+        <v>13.65507</v>
       </c>
       <c r="N37">
-        <v>29.82081</v>
+        <v>29.95367</v>
       </c>
       <c r="O37">
-        <v>34.38298</v>
+        <v>23.793</v>
       </c>
       <c r="P37">
-        <v>50.37292</v>
+        <v>38.99323</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
@@ -3060,13 +3060,13 @@
         <v>1</v>
       </c>
       <c r="D38">
-        <v>48.14</v>
+        <v>57.92</v>
       </c>
       <c r="E38">
-        <v>1.177</v>
+        <v>0.1903</v>
       </c>
       <c r="F38">
-        <v>0.56</v>
+        <v>0.11</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -3075,28 +3075,28 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>0.51208</v>
+        <v>7.67079</v>
       </c>
       <c r="J38">
-        <v>2.91953</v>
+        <v>4.31261</v>
       </c>
       <c r="K38">
-        <v>7.42109</v>
+        <v>-0.70348</v>
       </c>
       <c r="L38">
-        <v>7.71633</v>
+        <v>-8.63236</v>
       </c>
       <c r="M38">
-        <v>5.83161</v>
+        <v>-12.44342</v>
       </c>
       <c r="N38">
-        <v>27.23334</v>
+        <v>8.43033</v>
       </c>
       <c r="O38">
-        <v>21.00613</v>
+        <v>0.55188</v>
       </c>
       <c r="P38">
-        <v>37.24302</v>
+        <v>27.94261</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -3110,13 +3110,13 @@
         <v>1</v>
       </c>
       <c r="D39">
-        <v>43.87</v>
+        <v>87.97</v>
       </c>
       <c r="E39">
-        <v>1.1762</v>
+        <v>0.1659</v>
       </c>
       <c r="F39">
-        <v>0.51</v>
+        <v>0.1457</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -3125,28 +3125,28 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>4.07033</v>
+        <v>2.47358</v>
       </c>
       <c r="J39">
-        <v>6.06284</v>
+        <v>3.61212</v>
       </c>
       <c r="K39">
-        <v>4.90863</v>
+        <v>5.36888</v>
       </c>
       <c r="L39">
-        <v>6.56576</v>
+        <v>6.01945</v>
       </c>
       <c r="M39">
-        <v>7.44443</v>
+        <v>9.75633</v>
       </c>
       <c r="N39">
-        <v>26.06225</v>
+        <v>27.18439</v>
       </c>
       <c r="O39">
-        <v>15.41584</v>
+        <v>21.02679</v>
       </c>
       <c r="P39">
-        <v>33.36677</v>
+        <v>34.46583</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
@@ -3160,43 +3160,43 @@
         <v>1</v>
       </c>
       <c r="D40">
-        <v>64.7122</v>
+        <v>84.67</v>
       </c>
       <c r="E40">
-        <v>1.1444</v>
+        <v>0.1538</v>
       </c>
       <c r="F40">
-        <v>0.7322</v>
+        <v>0.13</v>
       </c>
       <c r="G40">
-        <v>0.00030906168870136673</v>
+        <v>0.0709136035929586</v>
       </c>
       <c r="H40">
-        <v>0.00019999999999242846</v>
+        <v>0.060000000000002274</v>
       </c>
       <c r="I40">
-        <v>2.73107</v>
+        <v>3.69615</v>
       </c>
       <c r="J40">
-        <v>0.23479</v>
+        <v>3.35871</v>
       </c>
       <c r="K40">
-        <v>4.20994</v>
+        <v>5.47618</v>
       </c>
       <c r="L40">
-        <v>7.67216</v>
+        <v>6.47052</v>
       </c>
       <c r="M40">
-        <v>13.21569</v>
+        <v>12.70852</v>
       </c>
       <c r="N40">
-        <v>25.76369</v>
+        <v>16.79108</v>
       </c>
       <c r="O40">
-        <v>21.46748</v>
+        <v>14.5952</v>
       </c>
       <c r="P40">
-        <v>46.03969</v>
+        <v>24.44096</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -3210,43 +3210,43 @@
         <v>1</v>
       </c>
       <c r="D41">
-        <v>84.88</v>
+        <v>46.0203</v>
       </c>
       <c r="E41">
-        <v>1.0947</v>
+        <v>0.1523</v>
       </c>
       <c r="F41">
-        <v>0.9191</v>
+        <v>0.07</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>0.0006518904823897177</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>0.0002999999999957481</v>
       </c>
       <c r="I41">
-        <v>4.92468</v>
+        <v>1.74837</v>
       </c>
       <c r="J41">
-        <v>2.44082</v>
+        <v>-0.36703</v>
       </c>
       <c r="K41">
-        <v>4.28667</v>
+        <v>2.29803</v>
       </c>
       <c r="L41">
-        <v>3.60813</v>
+        <v>5.83481</v>
       </c>
       <c r="M41">
-        <v>8.82453</v>
+        <v>12.59197</v>
       </c>
       <c r="N41">
-        <v>21.19883</v>
+        <v>27.11857</v>
       </c>
       <c r="O41">
-        <v>15.71876</v>
+        <v>22.46372</v>
       </c>
       <c r="P41">
-        <v>30.32089</v>
+        <v>43.85828</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
@@ -3260,43 +3260,43 @@
         <v>1</v>
       </c>
       <c r="D42">
-        <v>103.09</v>
+        <v>777.91</v>
       </c>
       <c r="E42">
-        <v>1.0884</v>
+        <v>0.1519</v>
       </c>
       <c r="F42">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>0.06753410472288213</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>0.5249999999999773</v>
       </c>
       <c r="I42">
-        <v>13.47363</v>
+        <v>3.58872</v>
       </c>
       <c r="J42">
-        <v>-3.53624</v>
+        <v>3.43988</v>
       </c>
       <c r="K42">
-        <v>2.16912</v>
+        <v>5.21119</v>
       </c>
       <c r="L42">
-        <v>10.32625</v>
+        <v>6.02845</v>
       </c>
       <c r="M42">
-        <v>49.43291</v>
+        <v>12.53871</v>
       </c>
       <c r="N42">
-        <v>61.41803</v>
+        <v>16.28352</v>
       </c>
       <c r="O42">
-        <v>59.9127</v>
+        <v>14.06843</v>
       </c>
       <c r="P42">
-        <v>79.75326</v>
+        <v>23.79502</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -3310,43 +3310,43 @@
         <v>1</v>
       </c>
       <c r="D43">
-        <v>45.4516</v>
+        <v>49.37</v>
       </c>
       <c r="E43">
-        <v>1.0822</v>
+        <v>0.1458</v>
       </c>
       <c r="F43">
-        <v>0.4866</v>
+        <v>0.0719</v>
       </c>
       <c r="G43">
-        <v>-0.0008800492827577835</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>-0.00039999999999906777</v>
+        <v>0</v>
       </c>
       <c r="I43">
-        <v>3.23684</v>
+        <v>3.82981</v>
       </c>
       <c r="J43">
-        <v>1.99685</v>
+        <v>3.48803</v>
       </c>
       <c r="K43">
-        <v>8.76227</v>
+        <v>5.83193</v>
       </c>
       <c r="L43">
-        <v>8.91001</v>
+        <v>3.91764</v>
       </c>
       <c r="M43">
-        <v>16.01739</v>
+        <v>11.6151</v>
       </c>
       <c r="N43">
-        <v>24.20581</v>
+        <v>11.03791</v>
       </c>
       <c r="O43">
-        <v>21.55726</v>
+        <v>10.69201</v>
       </c>
       <c r="P43">
-        <v>35.52216</v>
+        <v>16.45407</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
@@ -3360,13 +3360,13 @@
         <v>1</v>
       </c>
       <c r="D44">
-        <v>38.07</v>
+        <v>42.82</v>
       </c>
       <c r="E44">
-        <v>1.035</v>
+        <v>0.1403</v>
       </c>
       <c r="F44">
-        <v>0.39</v>
+        <v>0.06</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -3375,28 +3375,28 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>4.89024</v>
+        <v>7.6696</v>
       </c>
       <c r="J44">
-        <v>1.84917</v>
+        <v>4.30904</v>
       </c>
       <c r="K44">
-        <v>6.47807</v>
+        <v>-0.7096</v>
       </c>
       <c r="L44">
-        <v>5.31945</v>
+        <v>-8.63999</v>
       </c>
       <c r="M44">
-        <v>15.44144</v>
+        <v>-12.45744</v>
       </c>
       <c r="N44">
-        <v>27.39075</v>
+        <v>8.40806</v>
       </c>
       <c r="O44">
-        <v>23.44412</v>
+        <v>0.53475</v>
       </c>
       <c r="P44">
-        <v>37.40593</v>
+        <v>27.90949</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -3410,43 +3410,43 @@
         <v>1</v>
       </c>
       <c r="D45">
-        <v>83.44</v>
+        <v>58.24</v>
       </c>
       <c r="E45">
-        <v>1.0047</v>
+        <v>0.1376</v>
       </c>
       <c r="F45">
-        <v>0.83</v>
+        <v>0.08</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>0.08592541673827851</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>0.05000000000000426</v>
       </c>
       <c r="I45">
-        <v>8.25885</v>
+        <v>3.91272</v>
       </c>
       <c r="J45">
-        <v>3.08209</v>
+        <v>3.56943</v>
       </c>
       <c r="K45">
-        <v>5.62297</v>
+        <v>5.39807</v>
       </c>
       <c r="L45">
-        <v>11.31534</v>
+        <v>5.91485</v>
       </c>
       <c r="M45">
-        <v>25.4246</v>
+        <v>13.91392</v>
       </c>
       <c r="N45">
-        <v>21.99203</v>
+        <v>19.31287</v>
       </c>
       <c r="O45">
-        <v>22.04621</v>
+        <v>16.15018</v>
       </c>
       <c r="P45">
-        <v>36.37611</v>
+        <v>27.1855</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
@@ -3460,43 +3460,43 @@
         <v>1</v>
       </c>
       <c r="D46">
-        <v>105.77</v>
+        <v>59.805</v>
       </c>
       <c r="E46">
-        <v>0.9737</v>
+        <v>0.1088</v>
       </c>
       <c r="F46">
-        <v>1.02</v>
+        <v>0.065</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>0.06693440428380046</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>0.03999999999999915</v>
       </c>
       <c r="I46">
-        <v>1.5608</v>
+        <v>3.86105</v>
       </c>
       <c r="J46">
-        <v>4.48287</v>
+        <v>1.89866</v>
       </c>
       <c r="K46">
-        <v>5.46301</v>
+        <v>3.79186</v>
       </c>
       <c r="L46">
-        <v>5.5637</v>
+        <v>3.8871</v>
       </c>
       <c r="M46">
-        <v>11.49107</v>
+        <v>9.26617</v>
       </c>
       <c r="N46">
-        <v>24.23774</v>
+        <v>12.99949</v>
       </c>
       <c r="O46">
-        <v>13.62367</v>
+        <v>10.13123</v>
       </c>
       <c r="P46">
-        <v>28.35263</v>
+        <v>21.44747</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
@@ -3510,13 +3510,13 @@
         <v>1</v>
       </c>
       <c r="D47">
-        <v>78.885</v>
+        <v>40.27</v>
       </c>
       <c r="E47">
-        <v>0.947</v>
+        <v>0.0994</v>
       </c>
       <c r="F47">
-        <v>0.74</v>
+        <v>0.04</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -3525,28 +3525,28 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>0.63283</v>
+        <v>1.74662</v>
       </c>
       <c r="J47">
-        <v>1.9095</v>
+        <v>2.27457</v>
       </c>
       <c r="K47">
-        <v>4.14594</v>
+        <v>3.60071</v>
       </c>
       <c r="L47">
-        <v>3.27031</v>
+        <v>4.16892</v>
       </c>
       <c r="M47">
-        <v>9.95913</v>
+        <v>8.70086</v>
       </c>
       <c r="N47">
-        <v>28.94745</v>
+        <v>12.27856</v>
       </c>
       <c r="O47">
-        <v>20.88957</v>
+        <v>9.88194</v>
       </c>
       <c r="P47">
-        <v>38.25933</v>
+        <v>16.83218</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
@@ -3560,43 +3560,43 @@
         <v>1</v>
       </c>
       <c r="D48">
-        <v>84.448</v>
+        <v>93.48</v>
       </c>
       <c r="E48">
-        <v>0.9366</v>
+        <v>0.091</v>
       </c>
       <c r="F48">
-        <v>0.7836</v>
+        <v>0.085</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>-0.058801518148278845</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>-0.05499999999999261</v>
       </c>
       <c r="I48">
-        <v>0.58547</v>
+        <v>3.2272</v>
       </c>
       <c r="J48">
-        <v>4.2731</v>
+        <v>3.54102</v>
       </c>
       <c r="K48">
-        <v>4.72991</v>
+        <v>5.97272</v>
       </c>
       <c r="L48">
-        <v>6.04346</v>
+        <v>7.61968</v>
       </c>
       <c r="M48">
-        <v>6.78029</v>
+        <v>12.97999</v>
       </c>
       <c r="N48">
-        <v>19.59446</v>
+        <v>19.46287</v>
       </c>
       <c r="O48">
-        <v>13.8773</v>
+        <v>15.86857</v>
       </c>
       <c r="P48">
-        <v>22.98002</v>
+        <v>29.8093</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
@@ -3610,13 +3610,13 @@
         <v>1</v>
       </c>
       <c r="D49">
-        <v>32.65</v>
+        <v>67.42</v>
       </c>
       <c r="E49">
-        <v>0.9274</v>
+        <v>0.0891</v>
       </c>
       <c r="F49">
-        <v>0.3</v>
+        <v>0.06</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -3625,28 +3625,28 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>0.09853</v>
+        <v>9.55922</v>
       </c>
       <c r="J49">
-        <v>5.92234</v>
+        <v>6.69536</v>
       </c>
       <c r="K49">
-        <v>4.09211</v>
+        <v>3.25035</v>
       </c>
       <c r="L49">
-        <v>-0.40394</v>
+        <v>-3.4282</v>
       </c>
       <c r="M49">
-        <v>19.45838</v>
+        <v>-3.78501</v>
       </c>
       <c r="N49">
-        <v>30.36594</v>
+        <v>18.29687</v>
       </c>
       <c r="O49">
-        <v>29.70693</v>
+        <v>9.16935</v>
       </c>
       <c r="P49">
-        <v>41.31571</v>
+        <v>43.34337</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
@@ -3660,13 +3660,13 @@
         <v>1</v>
       </c>
       <c r="D50">
-        <v>40.54</v>
+        <v>60.43</v>
       </c>
       <c r="E50">
-        <v>0.896</v>
+        <v>0.0828</v>
       </c>
       <c r="F50">
-        <v>0.36</v>
+        <v>0.05</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -3675,28 +3675,28 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>3.27996</v>
+        <v>2.48981</v>
       </c>
       <c r="J50">
-        <v>2.06738</v>
+        <v>2.67332</v>
       </c>
       <c r="K50">
-        <v>-1.03935</v>
+        <v>5.1599</v>
       </c>
       <c r="L50">
-        <v>-5.07952</v>
+        <v>5.09281</v>
       </c>
       <c r="M50">
-        <v>4.54902</v>
+        <v>10.79128</v>
       </c>
       <c r="N50">
-        <v>19.51019</v>
+        <v>16.67663</v>
       </c>
       <c r="O50">
-        <v>14.61737</v>
+        <v>13.81225</v>
       </c>
       <c r="P50">
-        <v>28.15624</v>
+        <v>21.97019</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
@@ -3710,43 +3710,43 @@
         <v>1</v>
       </c>
       <c r="D51">
-        <v>47.64</v>
+        <v>65.9499</v>
       </c>
       <c r="E51">
-        <v>0.8895</v>
+        <v>0.0821</v>
       </c>
       <c r="F51">
-        <v>0.42</v>
+        <v>0.0541</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>-0.000151630022749537</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>-0.00010000000000331966</v>
       </c>
       <c r="I51">
-        <v>2.34846</v>
+        <v>3.26326</v>
       </c>
       <c r="J51">
-        <v>1.87475</v>
+        <v>3.6046</v>
       </c>
       <c r="K51">
-        <v>6.47144</v>
+        <v>5.71401</v>
       </c>
       <c r="L51">
-        <v>8.45324</v>
+        <v>6.01896</v>
       </c>
       <c r="M51">
-        <v>11.26274</v>
+        <v>11.42488</v>
       </c>
       <c r="N51">
-        <v>18.88113</v>
+        <v>17.97829</v>
       </c>
       <c r="O51">
-        <v>15.78963</v>
+        <v>14.93646</v>
       </c>
       <c r="P51">
-        <v>29.11428</v>
+        <v>21.29822</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
@@ -3760,13 +3760,13 @@
         <v>1</v>
       </c>
       <c r="D52">
-        <v>40.143</v>
+        <v>126.97</v>
       </c>
       <c r="E52">
-        <v>0.8618</v>
+        <v>0.0788</v>
       </c>
       <c r="F52">
-        <v>0.343</v>
+        <v>0.1</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -3775,28 +3775,28 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>3.96371</v>
+        <v>1.27686</v>
       </c>
       <c r="J52">
-        <v>3.51807</v>
+        <v>3.04903</v>
       </c>
       <c r="K52">
-        <v>5.62678</v>
+        <v>6.35333</v>
       </c>
       <c r="L52">
-        <v>9.83214</v>
+        <v>6.81078</v>
       </c>
       <c r="M52">
-        <v>11.16139</v>
+        <v>10.85416</v>
       </c>
       <c r="N52">
-        <v>30.07894</v>
+        <v>31.04129</v>
       </c>
       <c r="O52">
-        <v>18.72822</v>
+        <v>25.18451</v>
       </c>
       <c r="P52">
-        <v>39.49437</v>
+        <v>39.56144</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
@@ -3810,13 +3810,13 @@
         <v>1</v>
       </c>
       <c r="D53">
-        <v>241.05</v>
+        <v>42.055</v>
       </c>
       <c r="E53">
-        <v>0.8324</v>
+        <v>0.0688</v>
       </c>
       <c r="F53">
-        <v>1.99</v>
+        <v>0.0289</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -3825,28 +3825,28 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>2.77183</v>
+        <v>1.65988</v>
       </c>
       <c r="J53">
-        <v>2.96822</v>
+        <v>2.02083</v>
       </c>
       <c r="K53">
-        <v>5.67531</v>
+        <v>3.36434</v>
       </c>
       <c r="L53">
-        <v>8.36877</v>
+        <v>3.95573</v>
       </c>
       <c r="M53">
-        <v>13.7945</v>
+        <v>8.0455</v>
       </c>
       <c r="N53">
-        <v>21.79801</v>
+        <v>12.75886</v>
       </c>
       <c r="O53">
-        <v>17.66382</v>
+        <v>10.15857</v>
       </c>
       <c r="P53">
-        <v>28.37503</v>
+        <v>17.60678</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
@@ -3860,13 +3860,13 @@
         <v>1</v>
       </c>
       <c r="D54">
-        <v>184.99</v>
+        <v>90.78</v>
       </c>
       <c r="E54">
-        <v>0.812</v>
+        <v>0.0441</v>
       </c>
       <c r="F54">
-        <v>1.49</v>
+        <v>0.04</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -3875,28 +3875,28 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>1.94303</v>
+        <v>5.02797</v>
       </c>
       <c r="J54">
-        <v>4.13894</v>
+        <v>7.92296</v>
       </c>
       <c r="K54">
-        <v>8.00371</v>
+        <v>16.70934</v>
       </c>
       <c r="L54">
-        <v>9.63229</v>
+        <v>12.60463</v>
       </c>
       <c r="M54">
-        <v>16.33092</v>
+        <v>5.4508</v>
       </c>
       <c r="N54">
-        <v>29.76918</v>
+        <v>49.27709</v>
       </c>
       <c r="O54">
-        <v>23.74609</v>
+        <v>28.7887</v>
       </c>
       <c r="P54">
-        <v>39.19834</v>
+        <v>81.58936</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
@@ -3910,43 +3910,43 @@
         <v>1</v>
       </c>
       <c r="D55">
-        <v>99.05</v>
+        <v>157.36</v>
       </c>
       <c r="E55">
-        <v>0.7835</v>
+        <v>0.0254</v>
       </c>
       <c r="F55">
-        <v>0.77</v>
+        <v>0.04</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>0.08901322482196487</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>0.13999999999998636</v>
       </c>
       <c r="I55">
-        <v>13.67456</v>
+        <v>7.02074</v>
       </c>
       <c r="J55">
-        <v>-6.05846</v>
+        <v>-3.96718</v>
       </c>
       <c r="K55">
-        <v>-3.29711</v>
+        <v>22.35728</v>
       </c>
       <c r="L55">
-        <v>11.22243</v>
+        <v>17.83303</v>
       </c>
       <c r="M55">
-        <v>48.94153</v>
+        <v>25.48645</v>
       </c>
       <c r="N55">
-        <v>64.71321</v>
+        <v>45.02857</v>
       </c>
       <c r="O55">
-        <v>60.48098</v>
+        <v>29.15713</v>
       </c>
       <c r="P55">
-        <v>84.19497</v>
+        <v>85.26304</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
@@ -3960,43 +3960,43 @@
         <v>1</v>
       </c>
       <c r="D56">
-        <v>65.8958</v>
+        <v>74.38</v>
       </c>
       <c r="E56">
-        <v>0.7763</v>
+        <v>0.0523</v>
       </c>
       <c r="F56">
-        <v>0.5076</v>
+        <v>0.0389</v>
       </c>
       <c r="G56">
-        <v>-0.00030350855895143757</v>
+        <v>-0.18786902844873937</v>
       </c>
       <c r="H56">
-        <v>-0.0002000000000066393</v>
+        <v>-0.14000000000000057</v>
       </c>
       <c r="I56">
-        <v>3.2024</v>
+        <v>-0.33512</v>
       </c>
       <c r="J56">
-        <v>2.52312</v>
+        <v>4.32159</v>
       </c>
       <c r="K56">
-        <v>5.07157</v>
+        <v>7.46963</v>
       </c>
       <c r="L56">
-        <v>5.35778</v>
+        <v>8.26408</v>
       </c>
       <c r="M56">
-        <v>10.74773</v>
+        <v>7.59443</v>
       </c>
       <c r="N56">
-        <v>17.67803</v>
+        <v>24.30679</v>
       </c>
       <c r="O56">
-        <v>14.23797</v>
+        <v>17.17142</v>
       </c>
       <c r="P56">
-        <v>20.56107</v>
+        <v>36.70093</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
@@ -4010,43 +4010,43 @@
         <v>1</v>
       </c>
       <c r="D57">
-        <v>53.7006</v>
+        <v>50.29</v>
       </c>
       <c r="E57">
-        <v>0.7556</v>
+        <v>0.0398</v>
       </c>
       <c r="F57">
-        <v>0.4027</v>
+        <v>0.02</v>
       </c>
       <c r="G57">
-        <v>-0.0007448650863095059</v>
+        <v>0</v>
       </c>
       <c r="H57">
-        <v>-0.00039999999999906777</v>
+        <v>0</v>
       </c>
       <c r="I57">
-        <v>3.7512</v>
+        <v>2.65217</v>
       </c>
       <c r="J57">
-        <v>4.61167</v>
+        <v>2.83038</v>
       </c>
       <c r="K57">
-        <v>5.5364</v>
+        <v>7.57811</v>
       </c>
       <c r="L57">
-        <v>5.829</v>
+        <v>10.32631</v>
       </c>
       <c r="M57">
-        <v>7.49084</v>
+        <v>11.68866</v>
       </c>
       <c r="N57">
-        <v>23.53788</v>
+        <v>20.90296</v>
       </c>
       <c r="O57">
-        <v>14.20511</v>
+        <v>16.87427</v>
       </c>
       <c r="P57">
-        <v>28.93499</v>
+        <v>27.10058</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
@@ -4060,43 +4060,43 @@
         <v>1</v>
       </c>
       <c r="D58">
-        <v>46.09</v>
+        <v>73.9399</v>
       </c>
       <c r="E58">
-        <v>0.7542</v>
+        <v>0.0283</v>
       </c>
       <c r="F58">
-        <v>0.345</v>
+        <v>0.0209</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>-0.00013524479307995628</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>-0.00010000000000331966</v>
       </c>
       <c r="I58">
-        <v>3.88397</v>
+        <v>1.93058</v>
       </c>
       <c r="J58">
-        <v>0.85996</v>
+        <v>1.99695</v>
       </c>
       <c r="K58">
-        <v>4.34821</v>
+        <v>3.48469</v>
       </c>
       <c r="L58">
-        <v>6.01695</v>
+        <v>3.64148</v>
       </c>
       <c r="M58">
-        <v>12.18119</v>
+        <v>7.10472</v>
       </c>
       <c r="N58">
-        <v>20.20441</v>
+        <v>15.68906</v>
       </c>
       <c r="O58">
-        <v>17.42608</v>
+        <v>12.70804</v>
       </c>
       <c r="P58">
-        <v>32.64341</v>
+        <v>20.9949</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
@@ -4110,43 +4110,43 @@
         <v>1</v>
       </c>
       <c r="D59">
-        <v>20.4931</v>
+        <v>37.34</v>
       </c>
       <c r="E59">
-        <v>0.7527</v>
+        <v>0.0268</v>
       </c>
       <c r="F59">
-        <v>0.1531</v>
+        <v>0.01</v>
       </c>
       <c r="G59">
-        <v>0.0004879715024631189</v>
+        <v>0</v>
       </c>
       <c r="H59">
-        <v>0.00009999999999976694</v>
+        <v>0</v>
       </c>
       <c r="I59">
-        <v>1.44855</v>
+        <v>1.49619</v>
       </c>
       <c r="J59">
-        <v>7.40349</v>
+        <v>1.99563</v>
       </c>
       <c r="K59">
-        <v>9.00149</v>
+        <v>3.15178</v>
       </c>
       <c r="L59">
-        <v>7.71186</v>
+        <v>3.81191</v>
       </c>
       <c r="M59">
-        <v>13.27869</v>
+        <v>7.89474</v>
       </c>
       <c r="N59">
-        <v>31.09302</v>
+        <v>11.20715</v>
       </c>
       <c r="O59">
-        <v>20.14406</v>
+        <v>8.90251</v>
       </c>
       <c r="P59">
-        <v>36.96373</v>
+        <v>15.36797</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
@@ -4160,13 +4160,13 @@
         <v>1</v>
       </c>
       <c r="D60">
-        <v>35.01</v>
+        <v>241.09</v>
       </c>
       <c r="E60">
-        <v>0.7482</v>
+        <v>0.0166</v>
       </c>
       <c r="F60">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -4175,28 +4175,28 @@
         <v>0</v>
       </c>
       <c r="I60">
-        <v>0.40509</v>
+        <v>3.54305</v>
       </c>
       <c r="J60">
-        <v>6.44172</v>
+        <v>3.86613</v>
       </c>
       <c r="K60">
-        <v>6.40033</v>
+        <v>6.19127</v>
       </c>
       <c r="L60">
-        <v>5.03744</v>
+        <v>9.3549</v>
       </c>
       <c r="M60">
-        <v>8.21639</v>
+        <v>14.3501</v>
       </c>
       <c r="N60">
-        <v>23.65655</v>
+        <v>22.13509</v>
       </c>
       <c r="O60">
-        <v>16.82654</v>
+        <v>18.23831</v>
       </c>
       <c r="P60">
-        <v>30.11889</v>
+        <v>28.91367</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
@@ -4210,43 +4210,43 @@
         <v>1</v>
       </c>
       <c r="D61">
-        <v>49.2981</v>
+        <v>117.42</v>
       </c>
       <c r="E61">
-        <v>0.7369</v>
+        <v>0.0128</v>
       </c>
       <c r="F61">
-        <v>0.3606</v>
+        <v>0.015</v>
       </c>
       <c r="G61">
-        <v>0.00020284798571182245</v>
+        <v>-0.0638325035107901</v>
       </c>
       <c r="H61">
-        <v>0.00009999999999621423</v>
+        <v>-0.07500000000000284</v>
       </c>
       <c r="I61">
-        <v>5.66156</v>
+        <v>4.96384</v>
       </c>
       <c r="J61">
-        <v>3.81333</v>
+        <v>3.08608</v>
       </c>
       <c r="K61">
-        <v>5.3725</v>
+        <v>4.54905</v>
       </c>
       <c r="L61">
-        <v>4.38278</v>
+        <v>5.00354</v>
       </c>
       <c r="M61">
-        <v>14.21529</v>
+        <v>12.4997</v>
       </c>
       <c r="N61">
-        <v>9.46193</v>
+        <v>22.97832</v>
       </c>
       <c r="O61">
-        <v>10.21148</v>
+        <v>21.42941</v>
       </c>
       <c r="P61">
-        <v>17.14976</v>
+        <v>27.97618</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
@@ -4260,13 +4260,13 @@
         <v>1</v>
       </c>
       <c r="D62">
-        <v>50.61</v>
+        <v>99.13</v>
       </c>
       <c r="E62">
-        <v>0.7365</v>
+        <v>0</v>
       </c>
       <c r="F62">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -4275,28 +4275,28 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>2.91896</v>
+        <v>4.1993</v>
       </c>
       <c r="J62">
-        <v>5.63982</v>
+        <v>2.25937</v>
       </c>
       <c r="K62">
-        <v>5.92712</v>
+        <v>7.33807</v>
       </c>
       <c r="L62">
-        <v>13.29864</v>
+        <v>10.57377</v>
       </c>
       <c r="M62">
-        <v>19.74092</v>
+        <v>20.05242</v>
       </c>
       <c r="N62">
-        <v>28.73674</v>
+        <v>22.6355</v>
       </c>
       <c r="O62">
-        <v>22.65721</v>
+        <v>24.39132</v>
       </c>
       <c r="P62">
-        <v>42.82279</v>
+        <v>23.63404</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
@@ -4310,43 +4310,43 @@
         <v>1</v>
       </c>
       <c r="D63">
-        <v>41.72</v>
+        <v>40.28</v>
       </c>
       <c r="E63">
-        <v>0.7243</v>
+        <v>-0.0248</v>
       </c>
       <c r="F63">
-        <v>0.3</v>
+        <v>-0.01</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>0.02483238142537375</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>0.00999999999999801</v>
       </c>
       <c r="I63">
-        <v>6.79818</v>
+        <v>1.60925</v>
       </c>
       <c r="J63">
-        <v>-2.01784</v>
+        <v>4.45391</v>
       </c>
       <c r="K63">
-        <v>-0.02896</v>
+        <v>7.60281</v>
       </c>
       <c r="L63">
-        <v>0.18738</v>
+        <v>7.93925</v>
       </c>
       <c r="M63">
-        <v>12.64137</v>
+        <v>9.15119</v>
       </c>
       <c r="N63">
-        <v>21.78693</v>
+        <v>29.85162</v>
       </c>
       <c r="O63">
-        <v>20.71114</v>
+        <v>23.37824</v>
       </c>
       <c r="P63">
-        <v>38.59393</v>
+        <v>37.60471</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
@@ -4360,13 +4360,13 @@
         <v>1</v>
       </c>
       <c r="D64">
-        <v>194.19</v>
+        <v>132.27</v>
       </c>
       <c r="E64">
-        <v>0.7053</v>
+        <v>-0.0378</v>
       </c>
       <c r="F64">
-        <v>1.36</v>
+        <v>-0.05</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -4375,28 +4375,28 @@
         <v>0</v>
       </c>
       <c r="I64">
-        <v>9.11779</v>
+        <v>5.00693</v>
       </c>
       <c r="J64">
-        <v>3.98803</v>
+        <v>-2.36275</v>
       </c>
       <c r="K64">
-        <v>4.97525</v>
+        <v>-3.27589</v>
       </c>
       <c r="L64">
-        <v>7.48768</v>
+        <v>0.07498</v>
       </c>
       <c r="M64">
-        <v>19.49266</v>
+        <v>18.22686</v>
       </c>
       <c r="N64">
-        <v>15.10471</v>
+        <v>25.70268</v>
       </c>
       <c r="O64">
-        <v>15.18194</v>
+        <v>26.24956</v>
       </c>
       <c r="P64">
-        <v>25.6483</v>
+        <v>42.89234</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
@@ -4410,13 +4410,13 @@
         <v>1</v>
       </c>
       <c r="D65">
-        <v>67.3</v>
+        <v>42.75</v>
       </c>
       <c r="E65">
-        <v>0.7033</v>
+        <v>-0.0468</v>
       </c>
       <c r="F65">
-        <v>0.47</v>
+        <v>-0.02</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -4425,28 +4425,28 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <v>0.03307</v>
+        <v>1.49167</v>
       </c>
       <c r="J65">
-        <v>5.23888</v>
+        <v>1.88994</v>
       </c>
       <c r="K65">
-        <v>9.42618</v>
+        <v>3.21341</v>
       </c>
       <c r="L65">
-        <v>16.32404</v>
+        <v>3.76254</v>
       </c>
       <c r="M65">
-        <v>20.84852</v>
+        <v>9.22817</v>
       </c>
       <c r="N65">
-        <v>31.49247</v>
+        <v>12.94479</v>
       </c>
       <c r="O65">
-        <v>27.03697</v>
+        <v>10.54485</v>
       </c>
       <c r="P65">
-        <v>37.16692</v>
+        <v>17.20701</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
@@ -4460,43 +4460,43 @@
         <v>1</v>
       </c>
       <c r="D66">
-        <v>56.4736</v>
+        <v>62.56</v>
       </c>
       <c r="E66">
-        <v>0.6843</v>
+        <v>-0.1596</v>
       </c>
       <c r="F66">
-        <v>0.3838</v>
+        <v>-0.1</v>
       </c>
       <c r="G66">
-        <v>-0.0007082905407781772</v>
+        <v>-0.02394636015325761</v>
       </c>
       <c r="H66">
-        <v>-0.00039999999999906777</v>
+        <v>-0.015000000000000568</v>
       </c>
       <c r="I66">
-        <v>4.48941</v>
+        <v>1.87628</v>
       </c>
       <c r="J66">
-        <v>-0.5182</v>
+        <v>4.56837</v>
       </c>
       <c r="K66">
-        <v>5.57613</v>
+        <v>12.11099</v>
       </c>
       <c r="L66">
-        <v>11.46197</v>
+        <v>11.57841</v>
       </c>
       <c r="M66">
-        <v>9.86297</v>
+        <v>12.65937</v>
       </c>
       <c r="N66">
-        <v>27.02674</v>
+        <v>27.71908</v>
       </c>
       <c r="O66">
-        <v>21.7608</v>
+        <v>18.12568</v>
       </c>
       <c r="P66">
-        <v>34.02071</v>
+        <v>37.90727</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
@@ -4510,13 +4510,13 @@
         <v>1</v>
       </c>
       <c r="D67">
-        <v>50.13</v>
+        <v>64.59</v>
       </c>
       <c r="E67">
-        <v>0.6843</v>
+        <v>-0.0582</v>
       </c>
       <c r="F67">
-        <v>0.3407</v>
+        <v>-0.0376</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -4525,28 +4525,28 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>8.48948</v>
+        <v>5.78832</v>
       </c>
       <c r="J67">
-        <v>2.4068</v>
+        <v>7.7204</v>
       </c>
       <c r="K67">
-        <v>1.61813</v>
+        <v>9.4579</v>
       </c>
       <c r="L67">
-        <v>2.81602</v>
+        <v>10.40516</v>
       </c>
       <c r="M67">
-        <v>11.5047</v>
+        <v>13.84191</v>
       </c>
       <c r="N67">
-        <v>5.70328</v>
+        <v>22.33689</v>
       </c>
       <c r="O67">
-        <v>6.60746</v>
+        <v>17.27653</v>
       </c>
       <c r="P67">
-        <v>17.62953</v>
+        <v>27.73559</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
@@ -4560,13 +4560,13 @@
         <v>1</v>
       </c>
       <c r="D68">
-        <v>84.55</v>
+        <v>46.225</v>
       </c>
       <c r="E68">
-        <v>0.6787</v>
+        <v>-0.0973</v>
       </c>
       <c r="F68">
-        <v>0.57</v>
+        <v>-0.045</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -4575,28 +4575,28 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>5.63531</v>
+        <v>5.20928</v>
       </c>
       <c r="J68">
-        <v>3.0173</v>
+        <v>2.59539</v>
       </c>
       <c r="K68">
-        <v>4.94015</v>
+        <v>5.9294</v>
       </c>
       <c r="L68">
-        <v>6.90542</v>
+        <v>11.41466</v>
       </c>
       <c r="M68">
-        <v>14.50115</v>
+        <v>20.3668</v>
       </c>
       <c r="N68">
-        <v>15.0701</v>
+        <v>27.15216</v>
       </c>
       <c r="O68">
-        <v>14.01283</v>
+        <v>25.82613</v>
       </c>
       <c r="P68">
-        <v>24.59179</v>
+        <v>39.39145</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
@@ -4610,43 +4610,43 @@
         <v>1</v>
       </c>
       <c r="D69">
-        <v>99.39</v>
+        <v>253.8</v>
       </c>
       <c r="E69">
-        <v>0.6787</v>
+        <v>-0.0866</v>
       </c>
       <c r="F69">
-        <v>0.67</v>
+        <v>-0.22</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>0.16180591183552034</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>0.410000000000025</v>
       </c>
       <c r="I69">
-        <v>4.25442</v>
+        <v>6.68433</v>
       </c>
       <c r="J69">
-        <v>2.1911</v>
+        <v>4.37309</v>
       </c>
       <c r="K69">
-        <v>3.98921</v>
+        <v>5.35685</v>
       </c>
       <c r="L69">
-        <v>4.7615</v>
+        <v>9.42759</v>
       </c>
       <c r="M69">
-        <v>9.92675</v>
+        <v>31.35604</v>
       </c>
       <c r="N69">
-        <v>13.46996</v>
+        <v>27.45055</v>
       </c>
       <c r="O69">
-        <v>11.63428</v>
+        <v>27.3205</v>
       </c>
       <c r="P69">
-        <v>21.07926</v>
+        <v>39.66999</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
@@ -4660,43 +4660,43 @@
         <v>1</v>
       </c>
       <c r="D70">
-        <v>55.07</v>
+        <v>104.98</v>
       </c>
       <c r="E70">
-        <v>0.6764</v>
+        <v>-0.0952</v>
       </c>
       <c r="F70">
-        <v>0.37</v>
+        <v>-0.1</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>0.019054878048790237</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>0.020000000000010232</v>
       </c>
       <c r="I70">
-        <v>7.94118</v>
+        <v>5.17019</v>
       </c>
       <c r="J70">
-        <v>1.66396</v>
+        <v>3.3957</v>
       </c>
       <c r="K70">
-        <v>4.57581</v>
+        <v>3.93399</v>
       </c>
       <c r="L70">
-        <v>7.07393</v>
+        <v>3.63701</v>
       </c>
       <c r="M70">
-        <v>20.02841</v>
+        <v>16.31926</v>
       </c>
       <c r="N70">
-        <v>21.35007</v>
+        <v>16.68799</v>
       </c>
       <c r="O70">
-        <v>19.79413</v>
+        <v>15.36328</v>
       </c>
       <c r="P70">
-        <v>29.10031</v>
+        <v>26.52421</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
@@ -4710,43 +4710,43 @@
         <v>1</v>
       </c>
       <c r="D71">
-        <v>58.16</v>
+        <v>101.52</v>
       </c>
       <c r="E71">
-        <v>0.6751</v>
+        <v>0.0296</v>
       </c>
       <c r="F71">
-        <v>0.39</v>
+        <v>0.03</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>-0.07392075694853996</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>-0.07499999999998863</v>
       </c>
       <c r="I71">
-        <v>3.98811</v>
+        <v>2.66635</v>
       </c>
       <c r="J71">
-        <v>2.26336</v>
+        <v>3.0526</v>
       </c>
       <c r="K71">
-        <v>4.68165</v>
+        <v>5.13647</v>
       </c>
       <c r="L71">
-        <v>4.86399</v>
+        <v>5.56554</v>
       </c>
       <c r="M71">
-        <v>13.13962</v>
+        <v>10.73217</v>
       </c>
       <c r="N71">
-        <v>18.60459</v>
+        <v>23.15752</v>
       </c>
       <c r="O71">
-        <v>15.36068</v>
+        <v>18.90844</v>
       </c>
       <c r="P71">
-        <v>26.25907</v>
+        <v>30.44627</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
@@ -4760,43 +4760,43 @@
         <v>1</v>
       </c>
       <c r="D72">
-        <v>59.74</v>
+        <v>63.27</v>
       </c>
       <c r="E72">
-        <v>0.6741</v>
+        <v>-0.1389</v>
       </c>
       <c r="F72">
-        <v>0.4</v>
+        <v>-0.088</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>0.09489166534873048</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>0.060000000000002274</v>
       </c>
       <c r="I72">
-        <v>3.71219</v>
+        <v>2.86232</v>
       </c>
       <c r="J72">
-        <v>-0.21099</v>
+        <v>4.71698</v>
       </c>
       <c r="K72">
-        <v>3.09678</v>
+        <v>11.29207</v>
       </c>
       <c r="L72">
-        <v>3.07017</v>
+        <v>10.66733</v>
       </c>
       <c r="M72">
-        <v>8.53443</v>
+        <v>14.61082</v>
       </c>
       <c r="N72">
-        <v>12.09279</v>
+        <v>25.34576</v>
       </c>
       <c r="O72">
-        <v>9.3937</v>
+        <v>18.96323</v>
       </c>
       <c r="P72">
-        <v>20.94053</v>
+        <v>30.8947</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
@@ -4810,43 +4810,43 @@
         <v>1</v>
       </c>
       <c r="D73">
-        <v>146.19</v>
+        <v>109.5</v>
       </c>
       <c r="E73">
-        <v>0.6541</v>
+        <v>-0.1186</v>
       </c>
       <c r="F73">
-        <v>0.95</v>
+        <v>-0.13</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>0.03654302941714439</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>0.04000000000000625</v>
       </c>
       <c r="I73">
-        <v>6.39971</v>
+        <v>4.68147</v>
       </c>
       <c r="J73">
-        <v>5.72438</v>
+        <v>5.68037</v>
       </c>
       <c r="K73">
-        <v>5.29525</v>
+        <v>4.85827</v>
       </c>
       <c r="L73">
-        <v>6.92654</v>
+        <v>2.83849</v>
       </c>
       <c r="M73">
-        <v>15.38806</v>
+        <v>7.0491</v>
       </c>
       <c r="N73">
-        <v>17.02883</v>
+        <v>27.58549</v>
       </c>
       <c r="O73">
-        <v>15.13872</v>
+        <v>18.40168</v>
       </c>
       <c r="P73">
-        <v>31.95987</v>
+        <v>36.15346</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
@@ -4860,13 +4860,13 @@
         <v>1</v>
       </c>
       <c r="D74">
-        <v>93.395</v>
+        <v>56.19</v>
       </c>
       <c r="E74">
-        <v>0.652</v>
+        <v>-0.1244</v>
       </c>
       <c r="F74">
-        <v>0.605</v>
+        <v>-0.07</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -4875,28 +4875,28 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>4.92878</v>
+        <v>1.80761</v>
       </c>
       <c r="J74">
-        <v>3.73345</v>
+        <v>2.23106</v>
       </c>
       <c r="K74">
-        <v>5.67247</v>
+        <v>5.78575</v>
       </c>
       <c r="L74">
-        <v>8.27852</v>
+        <v>7.58923</v>
       </c>
       <c r="M74">
-        <v>15.21179</v>
+        <v>10.83861</v>
       </c>
       <c r="N74">
-        <v>17.99798</v>
+        <v>20.69106</v>
       </c>
       <c r="O74">
-        <v>15.54029</v>
+        <v>16.2077</v>
       </c>
       <c r="P74">
-        <v>30.19864</v>
+        <v>28.51882</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
@@ -4910,43 +4910,43 @@
         <v>1</v>
       </c>
       <c r="D75">
-        <v>157.83</v>
+        <v>38</v>
       </c>
       <c r="E75">
-        <v>0.6441</v>
+        <v>0</v>
       </c>
       <c r="F75">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>-0.17076054117955533</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>-0.06499999999999773</v>
       </c>
       <c r="I75">
-        <v>-0.30361</v>
+        <v>1.84942</v>
       </c>
       <c r="J75">
-        <v>0.91073</v>
+        <v>5.32791</v>
       </c>
       <c r="K75">
-        <v>5.54124</v>
+        <v>8.40929</v>
       </c>
       <c r="L75">
-        <v>6.56091</v>
+        <v>7.03874</v>
       </c>
       <c r="M75">
-        <v>4.67153</v>
+        <v>9.86797</v>
       </c>
       <c r="N75">
-        <v>17.43395</v>
+        <v>27.82347</v>
       </c>
       <c r="O75">
-        <v>14.38136</v>
+        <v>21.90542</v>
       </c>
       <c r="P75">
-        <v>16.83887</v>
+        <v>37.45298</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
@@ -4960,43 +4960,43 @@
         <v>1</v>
       </c>
       <c r="D76">
-        <v>56.26</v>
+        <v>89.74</v>
       </c>
       <c r="E76">
-        <v>0.644</v>
+        <v>-0.1447</v>
       </c>
       <c r="F76">
-        <v>0.36</v>
+        <v>-0.13</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>-0.07237904348311557</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>-0.06500000000001194</v>
       </c>
       <c r="I76">
-        <v>1.97879</v>
+        <v>4.29686</v>
       </c>
       <c r="J76">
-        <v>1.87817</v>
+        <v>2.6599</v>
       </c>
       <c r="K76">
-        <v>5.26097</v>
+        <v>7.10247</v>
       </c>
       <c r="L76">
-        <v>8.99531</v>
+        <v>7.93057</v>
       </c>
       <c r="M76">
-        <v>11.06198</v>
+        <v>13.48801</v>
       </c>
       <c r="N76">
-        <v>19.48795</v>
+        <v>22.84592</v>
       </c>
       <c r="O76">
-        <v>15.63122</v>
+        <v>20.76607</v>
       </c>
       <c r="P76">
-        <v>29.27386</v>
+        <v>31.39802</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
@@ -5010,43 +5010,43 @@
         <v>1</v>
       </c>
       <c r="D77">
-        <v>188.25</v>
+        <v>47.57</v>
       </c>
       <c r="E77">
-        <v>0.6415</v>
+        <v>-0.1469</v>
       </c>
       <c r="F77">
-        <v>1.2</v>
+        <v>-0.07</v>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>0.02102607232968463</v>
       </c>
       <c r="H77">
-        <v>0</v>
+        <v>0.00999999999999801</v>
       </c>
       <c r="I77">
-        <v>0.09132</v>
+        <v>2.42946</v>
       </c>
       <c r="J77">
-        <v>-1.2156</v>
+        <v>2.81433</v>
       </c>
       <c r="K77">
-        <v>4.21218</v>
+        <v>7.49037</v>
       </c>
       <c r="L77">
-        <v>5.03719</v>
+        <v>8.96808</v>
       </c>
       <c r="M77">
-        <v>5.4209</v>
+        <v>10.23116</v>
       </c>
       <c r="N77">
-        <v>9.14378</v>
+        <v>20.46092</v>
       </c>
       <c r="O77">
-        <v>4.95376</v>
+        <v>16.89774</v>
       </c>
       <c r="P77">
-        <v>9.03216</v>
+        <v>29.07748</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.25">
@@ -5060,43 +5060,43 @@
         <v>1</v>
       </c>
       <c r="D78">
-        <v>42.46</v>
+        <v>70</v>
       </c>
       <c r="E78">
-        <v>0.6161</v>
+        <v>-0.1498</v>
       </c>
       <c r="F78">
-        <v>0.26</v>
+        <v>-0.105</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>0.050025012506248245</v>
       </c>
       <c r="H78">
-        <v>0</v>
+        <v>0.03499999999999659</v>
       </c>
       <c r="I78">
-        <v>4.53616</v>
+        <v>2.26425</v>
       </c>
       <c r="J78">
-        <v>6.2163</v>
+        <v>1.96333</v>
       </c>
       <c r="K78">
-        <v>16.23345</v>
+        <v>3.42634</v>
       </c>
       <c r="L78">
-        <v>16.94785</v>
+        <v>3.23165</v>
       </c>
       <c r="M78">
-        <v>15.73017</v>
+        <v>6.37196</v>
       </c>
       <c r="N78">
-        <v>29.63303</v>
+        <v>10.9603</v>
       </c>
       <c r="O78">
-        <v>17.31304</v>
+        <v>9.19312</v>
       </c>
       <c r="P78">
-        <v>35.72929</v>
+        <v>16.17073</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
@@ -5110,13 +5110,13 @@
         <v>1</v>
       </c>
       <c r="D79">
-        <v>776.73</v>
+        <v>45.92</v>
       </c>
       <c r="E79">
-        <v>0.5958</v>
+        <v>-0.1522</v>
       </c>
       <c r="F79">
-        <v>4.6</v>
+        <v>-0.07</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -5125,28 +5125,28 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>5.58217</v>
+        <v>2.43941</v>
       </c>
       <c r="J79">
-        <v>3.27501</v>
+        <v>1.42217</v>
       </c>
       <c r="K79">
-        <v>4.74392</v>
+        <v>4.84549</v>
       </c>
       <c r="L79">
-        <v>6.6909</v>
+        <v>5.72253</v>
       </c>
       <c r="M79">
-        <v>14.24984</v>
+        <v>10.48277</v>
       </c>
       <c r="N79">
-        <v>14.62988</v>
+        <v>21.42428</v>
       </c>
       <c r="O79">
-        <v>13.56183</v>
+        <v>17.98569</v>
       </c>
       <c r="P79">
-        <v>24.04576</v>
+        <v>31.95291</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
@@ -5160,43 +5160,43 @@
         <v>1</v>
       </c>
       <c r="D80">
-        <v>58.69</v>
+        <v>98.44</v>
       </c>
       <c r="E80">
-        <v>0.5827</v>
+        <v>-0.1623</v>
       </c>
       <c r="F80">
-        <v>0.34</v>
+        <v>-0.16</v>
       </c>
       <c r="G80">
-        <v>0</v>
+        <v>-0.02031281738776764</v>
       </c>
       <c r="H80">
-        <v>0</v>
+        <v>-0.01999999999999602</v>
       </c>
       <c r="I80">
-        <v>6.67273</v>
+        <v>3.55289</v>
       </c>
       <c r="J80">
-        <v>2.62375</v>
+        <v>1.53454</v>
       </c>
       <c r="K80">
-        <v>3.71055</v>
+        <v>5.00306</v>
       </c>
       <c r="L80">
-        <v>2.48085</v>
+        <v>5.12278</v>
       </c>
       <c r="M80">
-        <v>11.26992</v>
+        <v>6.73467</v>
       </c>
       <c r="N80">
-        <v>23.55852</v>
+        <v>21.28184</v>
       </c>
       <c r="O80">
-        <v>23.0328</v>
+        <v>20.17455</v>
       </c>
       <c r="P80">
-        <v>29.96305</v>
+        <v>24.99975</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.25">
@@ -5210,13 +5210,13 @@
         <v>1</v>
       </c>
       <c r="D81">
-        <v>62.66</v>
+        <v>99.225</v>
       </c>
       <c r="E81">
-        <v>0.5778</v>
+        <v>-0.166</v>
       </c>
       <c r="F81">
-        <v>0.36</v>
+        <v>-0.165</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -5225,28 +5225,28 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>4.3288</v>
+        <v>2.80633</v>
       </c>
       <c r="J81">
-        <v>3.95081</v>
+        <v>2.63999</v>
       </c>
       <c r="K81">
-        <v>11.30652</v>
+        <v>4.46493</v>
       </c>
       <c r="L81">
-        <v>12.20199</v>
+        <v>4.30003</v>
       </c>
       <c r="M81">
-        <v>13.93168</v>
+        <v>8.54677</v>
       </c>
       <c r="N81">
-        <v>27.03281</v>
+        <v>14.50136</v>
       </c>
       <c r="O81">
-        <v>17.27806</v>
+        <v>12.14497</v>
       </c>
       <c r="P81">
-        <v>40.69012</v>
+        <v>20.77227</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
@@ -5260,43 +5260,43 @@
         <v>1</v>
       </c>
       <c r="D82">
-        <v>70.12</v>
+        <v>145.8999</v>
       </c>
       <c r="E82">
-        <v>0.5737</v>
+        <v>-0.1984</v>
       </c>
       <c r="F82">
-        <v>0.4</v>
+        <v>-0.2901</v>
       </c>
       <c r="G82">
-        <v>0</v>
+        <v>0.006785934608277475</v>
       </c>
       <c r="H82">
-        <v>0</v>
+        <v>0.009900000000016007</v>
       </c>
       <c r="I82">
-        <v>3.33537</v>
+        <v>3.43644</v>
       </c>
       <c r="J82">
-        <v>1.55134</v>
+        <v>5.5763</v>
       </c>
       <c r="K82">
-        <v>3.08263</v>
+        <v>6.05152</v>
       </c>
       <c r="L82">
-        <v>3.64216</v>
+        <v>6.00603</v>
       </c>
       <c r="M82">
-        <v>7.42129</v>
+        <v>13.94536</v>
       </c>
       <c r="N82">
-        <v>10.32549</v>
+        <v>19.23097</v>
       </c>
       <c r="O82">
-        <v>8.83025</v>
+        <v>15.9657</v>
       </c>
       <c r="P82">
-        <v>16.39024</v>
+        <v>31.10094</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
@@ -5310,13 +5310,13 @@
         <v>1</v>
       </c>
       <c r="D83">
-        <v>57.98</v>
+        <v>44.52</v>
       </c>
       <c r="E83">
-        <v>0.5724</v>
+        <v>-0.2017</v>
       </c>
       <c r="F83">
-        <v>0.33</v>
+        <v>-0.09</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -5325,28 +5325,28 @@
         <v>0</v>
       </c>
       <c r="I83">
-        <v>2.29654</v>
+        <v>1.89584</v>
       </c>
       <c r="J83">
-        <v>4.98209</v>
+        <v>3.67186</v>
       </c>
       <c r="K83">
-        <v>5.81091</v>
+        <v>8.05771</v>
       </c>
       <c r="L83">
-        <v>6.75927</v>
+        <v>6.9717</v>
       </c>
       <c r="M83">
-        <v>9.44021</v>
+        <v>5.86954</v>
       </c>
       <c r="N83">
-        <v>27.60336</v>
+        <v>19.17256</v>
       </c>
       <c r="O83">
-        <v>17.20991</v>
+        <v>16.9788</v>
       </c>
       <c r="P83">
-        <v>36.22229</v>
+        <v>24.76341</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.25">
@@ -5360,43 +5360,43 @@
         <v>1</v>
       </c>
       <c r="D84">
-        <v>257.56</v>
+        <v>214.7442</v>
       </c>
       <c r="E84">
-        <v>0.5622</v>
+        <v>-0.2072</v>
       </c>
       <c r="F84">
-        <v>1.44</v>
+        <v>-0.4458</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>0.00009313415043337151</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>0.0002000000000066393</v>
       </c>
       <c r="I84">
-        <v>2.74462</v>
+        <v>3.46414</v>
       </c>
       <c r="J84">
-        <v>3.75621</v>
+        <v>0.76787</v>
       </c>
       <c r="K84">
-        <v>8.74926</v>
+        <v>-4.50208</v>
       </c>
       <c r="L84">
-        <v>10.78146</v>
+        <v>-1.9833</v>
       </c>
       <c r="M84">
-        <v>16.83044</v>
+        <v>27.33193</v>
       </c>
       <c r="N84">
-        <v>27.03058</v>
+        <v>49.65806</v>
       </c>
       <c r="O84">
-        <v>22.69339</v>
+        <v>41.52825</v>
       </c>
       <c r="P84">
-        <v>33.82532</v>
+        <v>75.21636</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
@@ -5410,43 +5410,43 @@
         <v>1</v>
       </c>
       <c r="D85">
-        <v>101.49</v>
+        <v>220.04</v>
       </c>
       <c r="E85">
-        <v>0.5449</v>
+        <v>-0.8382</v>
       </c>
       <c r="F85">
-        <v>0.55</v>
+        <v>-1.86</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>0.02258559942181379</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>0.05000000000001137</v>
       </c>
       <c r="I85">
-        <v>4.14132</v>
+        <v>2.91852</v>
       </c>
       <c r="J85">
-        <v>2.63608</v>
+        <v>-2.59957</v>
       </c>
       <c r="K85">
-        <v>4.70568</v>
+        <v>-6.00076</v>
       </c>
       <c r="L85">
-        <v>5.6116</v>
+        <v>-6.64955</v>
       </c>
       <c r="M85">
-        <v>12.68822</v>
+        <v>9.89942</v>
       </c>
       <c r="N85">
-        <v>22.19171</v>
+        <v>25.93539</v>
       </c>
       <c r="O85">
-        <v>18.42122</v>
+        <v>27.03895</v>
       </c>
       <c r="P85">
-        <v>30.58865</v>
+        <v>35.37373</v>
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.25">
@@ -5460,43 +5460,43 @@
         <v>1</v>
       </c>
       <c r="D86">
-        <v>43.9471</v>
+        <v>42.36</v>
       </c>
       <c r="E86">
-        <v>0.5312</v>
+        <v>-0.2238</v>
       </c>
       <c r="F86">
-        <v>0.2322</v>
+        <v>-0.095</v>
       </c>
       <c r="G86">
-        <v>0.00022754681774913923</v>
+        <v>0</v>
       </c>
       <c r="H86">
-        <v>0.00009999999999621423</v>
+        <v>0</v>
       </c>
       <c r="I86">
-        <v>2.27404</v>
+        <v>1.75197</v>
       </c>
       <c r="J86">
-        <v>1.55984</v>
+        <v>5.98418</v>
       </c>
       <c r="K86">
-        <v>3.9403</v>
+        <v>16.67555</v>
       </c>
       <c r="L86">
-        <v>5.47569</v>
+        <v>15.68273</v>
       </c>
       <c r="M86">
-        <v>8.66137</v>
+        <v>14.17782</v>
       </c>
       <c r="N86">
-        <v>18.08921</v>
+        <v>29.5814</v>
       </c>
       <c r="O86">
-        <v>13.66023</v>
+        <v>17.75926</v>
       </c>
       <c r="P86">
-        <v>24.14759</v>
+        <v>32.10484</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
@@ -5510,13 +5510,13 @@
         <v>1</v>
       </c>
       <c r="D87">
-        <v>98.6</v>
+        <v>54.94</v>
       </c>
       <c r="E87">
-        <v>0.4892</v>
+        <v>-0.2361</v>
       </c>
       <c r="F87">
-        <v>0.48</v>
+        <v>-0.13</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -5525,28 +5525,28 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>3.92951</v>
+        <v>3.94712</v>
       </c>
       <c r="J87">
-        <v>-0.88419</v>
+        <v>2.41905</v>
       </c>
       <c r="K87">
-        <v>4.59192</v>
+        <v>4.55681</v>
       </c>
       <c r="L87">
-        <v>2.82123</v>
+        <v>6.5578</v>
       </c>
       <c r="M87">
-        <v>6.31675</v>
+        <v>16.19407</v>
       </c>
       <c r="N87">
-        <v>21.40905</v>
+        <v>22.29393</v>
       </c>
       <c r="O87">
-        <v>19.704</v>
+        <v>19.77237</v>
       </c>
       <c r="P87">
-        <v>24.37164</v>
+        <v>27.914</v>
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.25">
@@ -5560,43 +5560,43 @@
         <v>1</v>
       </c>
       <c r="D88">
-        <v>60.4</v>
+        <v>58.51</v>
       </c>
       <c r="E88">
-        <v>0.4824</v>
+        <v>-0.2472</v>
       </c>
       <c r="F88">
-        <v>0.29</v>
+        <v>-0.145</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>0.017094017094013692</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>0.00999999999999801</v>
       </c>
       <c r="I88">
-        <v>5.31239</v>
+        <v>4.15557</v>
       </c>
       <c r="J88">
-        <v>3.21878</v>
+        <v>3.87885</v>
       </c>
       <c r="K88">
-        <v>5.28393</v>
+        <v>3.6752</v>
       </c>
       <c r="L88">
-        <v>5.74152</v>
+        <v>3.4015</v>
       </c>
       <c r="M88">
-        <v>13.23848</v>
+        <v>7.40902</v>
       </c>
       <c r="N88">
-        <v>15.8336</v>
+        <v>23.87854</v>
       </c>
       <c r="O88">
-        <v>13.94649</v>
+        <v>22.99086</v>
       </c>
       <c r="P88">
-        <v>22.92094</v>
+        <v>29.8617</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.25">
@@ -5610,13 +5610,13 @@
         <v>1</v>
       </c>
       <c r="D89">
-        <v>114.79</v>
+        <v>356.16</v>
       </c>
       <c r="E89">
-        <v>0.4814</v>
+        <v>-0.2549</v>
       </c>
       <c r="F89">
-        <v>0.55</v>
+        <v>-0.91</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -5625,28 +5625,28 @@
         <v>0</v>
       </c>
       <c r="I89">
-        <v>-2.24192</v>
+        <v>3.5763</v>
       </c>
       <c r="J89">
-        <v>0.31681</v>
+        <v>1.528</v>
       </c>
       <c r="K89">
-        <v>4.96895</v>
+        <v>5.20214</v>
       </c>
       <c r="L89">
-        <v>6.84525</v>
+        <v>5.40992</v>
       </c>
       <c r="M89">
-        <v>14.45411</v>
+        <v>6.77377</v>
       </c>
       <c r="N89">
-        <v>19.97683</v>
+        <v>21.46042</v>
       </c>
       <c r="O89">
-        <v>19.45267</v>
+        <v>20.1272</v>
       </c>
       <c r="P89">
-        <v>23.76678</v>
+        <v>25.24777</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">
@@ -5660,13 +5660,13 @@
         <v>1</v>
       </c>
       <c r="D90">
-        <v>221.9</v>
+        <v>157.39</v>
       </c>
       <c r="E90">
-        <v>0.4663</v>
+        <v>-0.2725</v>
       </c>
       <c r="F90">
-        <v>1.03</v>
+        <v>-0.43</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -5675,28 +5675,28 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>12.52711</v>
+        <v>1.84043</v>
       </c>
       <c r="J90">
-        <v>-5.2124</v>
+        <v>1.45893</v>
       </c>
       <c r="K90">
-        <v>-5.44137</v>
+        <v>5.99383</v>
       </c>
       <c r="L90">
-        <v>-6.99041</v>
+        <v>7.01679</v>
       </c>
       <c r="M90">
-        <v>16.56567</v>
+        <v>4.12102</v>
       </c>
       <c r="N90">
-        <v>23.11979</v>
+        <v>17.27194</v>
       </c>
       <c r="O90">
-        <v>27.79496</v>
+        <v>14.87186</v>
       </c>
       <c r="P90">
-        <v>36.47884</v>
+        <v>16.84947</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.25">
@@ -5710,13 +5710,13 @@
         <v>1</v>
       </c>
       <c r="D91">
-        <v>67.38</v>
+        <v>43.81</v>
       </c>
       <c r="E91">
-        <v>0.4622</v>
+        <v>-0.2732</v>
       </c>
       <c r="F91">
-        <v>0.31</v>
+        <v>-0.12</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -5725,28 +5725,28 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>-1.71427</v>
+        <v>2.90817</v>
       </c>
       <c r="J91">
-        <v>0.16737</v>
+        <v>2.29655</v>
       </c>
       <c r="K91">
-        <v>3.27624</v>
+        <v>4.89133</v>
       </c>
       <c r="L91">
-        <v>3.41011</v>
+        <v>5.41504</v>
       </c>
       <c r="M91">
-        <v>11.98741</v>
+        <v>7.83933</v>
       </c>
       <c r="N91">
-        <v>19.08995</v>
+        <v>19.73605</v>
       </c>
       <c r="O91">
-        <v>18.8663</v>
+        <v>14.7002</v>
       </c>
       <c r="P91">
-        <v>22.73765</v>
+        <v>24.13001</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.25">
@@ -5760,43 +5760,43 @@
         <v>1</v>
       </c>
       <c r="D92">
-        <v>135.2885</v>
+        <v>60.83</v>
       </c>
       <c r="E92">
-        <v>0.4609</v>
+        <v>-0.4908</v>
       </c>
       <c r="F92">
-        <v>0.6207</v>
+        <v>-0.3</v>
       </c>
       <c r="G92">
-        <v>-0.0003695791971174128</v>
+        <v>-0.016404199475062352</v>
       </c>
       <c r="H92">
-        <v>-0.0004999999999881766</v>
+        <v>-0.00999999999999801</v>
       </c>
       <c r="I92">
-        <v>4.91573</v>
+        <v>0.95216</v>
       </c>
       <c r="J92">
-        <v>3.20217</v>
+        <v>-1.08291</v>
       </c>
       <c r="K92">
-        <v>4.97592</v>
+        <v>0.09721</v>
       </c>
       <c r="L92">
-        <v>6.77455</v>
+        <v>-0.4884</v>
       </c>
       <c r="M92">
-        <v>12.887</v>
+        <v>5.16216</v>
       </c>
       <c r="N92">
-        <v>15.22108</v>
+        <v>18.18536</v>
       </c>
       <c r="O92">
-        <v>13.08648</v>
+        <v>17.02278</v>
       </c>
       <c r="P92">
-        <v>23.85582</v>
+        <v>22.22838</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.25">
@@ -5810,13 +5810,13 @@
         <v>1</v>
       </c>
       <c r="D93">
-        <v>40.29</v>
+        <v>98.72</v>
       </c>
       <c r="E93">
-        <v>0.4488</v>
+        <v>-0.3332</v>
       </c>
       <c r="F93">
-        <v>0.18</v>
+        <v>-0.33</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -5825,28 +5825,28 @@
         <v>0</v>
       </c>
       <c r="I93">
-        <v>1.54928</v>
+        <v>4.19498</v>
       </c>
       <c r="J93">
-        <v>4.23094</v>
+        <v>-2.62068</v>
       </c>
       <c r="K93">
-        <v>7.6752</v>
+        <v>-4.21923</v>
       </c>
       <c r="L93">
-        <v>7.37882</v>
+        <v>5.36284</v>
       </c>
       <c r="M93">
-        <v>12.18566</v>
+        <v>47.77214</v>
       </c>
       <c r="N93">
-        <v>29.74996</v>
+        <v>64.51801</v>
       </c>
       <c r="O93">
-        <v>23.46124</v>
+        <v>58.95071</v>
       </c>
       <c r="P93">
-        <v>37.11119</v>
+        <v>78.99323</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.25">
@@ -5860,43 +5860,43 @@
         <v>1</v>
       </c>
       <c r="D94">
-        <v>87.8243</v>
+        <v>84.69</v>
       </c>
       <c r="E94">
-        <v>0.428</v>
+        <v>-0.2238</v>
       </c>
       <c r="F94">
-        <v>0.3743</v>
+        <v>-0.19</v>
       </c>
       <c r="G94">
-        <v>0.00034159227545516957</v>
+        <v>-0.11807769512338448</v>
       </c>
       <c r="H94">
-        <v>0.0002999999999957481</v>
+        <v>-0.09999999999999432</v>
       </c>
       <c r="I94">
-        <v>3.18827</v>
+        <v>3.37905</v>
       </c>
       <c r="J94">
-        <v>2.98008</v>
+        <v>3.55756</v>
       </c>
       <c r="K94">
-        <v>4.82607</v>
+        <v>5.28287</v>
       </c>
       <c r="L94">
-        <v>5.55195</v>
+        <v>3.43185</v>
       </c>
       <c r="M94">
-        <v>11.70482</v>
+        <v>7.371</v>
       </c>
       <c r="N94">
-        <v>26.58321</v>
+        <v>22.36503</v>
       </c>
       <c r="O94">
-        <v>20.40332</v>
+        <v>16.82417</v>
       </c>
       <c r="P94">
-        <v>34.35474</v>
+        <v>29.79034</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.25">
@@ -5910,43 +5910,43 @@
         <v>1</v>
       </c>
       <c r="D95">
-        <v>58.68</v>
+        <v>57.79</v>
       </c>
       <c r="E95">
-        <v>0.4107</v>
+        <v>-0.3449</v>
       </c>
       <c r="F95">
-        <v>0.24</v>
+        <v>-0.2</v>
       </c>
       <c r="G95">
-        <v>0</v>
+        <v>0.03462004500605161</v>
       </c>
       <c r="H95">
-        <v>0</v>
+        <v>0.01999999999999602</v>
       </c>
       <c r="I95">
-        <v>5.05242</v>
+        <v>0.97196</v>
       </c>
       <c r="J95">
-        <v>-2.98592</v>
+        <v>4.48194</v>
       </c>
       <c r="K95">
-        <v>1.49087</v>
+        <v>6.3489</v>
       </c>
       <c r="L95">
-        <v>-0.66329</v>
+        <v>6.1681</v>
       </c>
       <c r="M95">
-        <v>9.55118</v>
+        <v>8.70816</v>
       </c>
       <c r="N95">
-        <v>34.47484</v>
+        <v>27.01884</v>
       </c>
       <c r="O95">
-        <v>32.16558</v>
+        <v>17.80586</v>
       </c>
       <c r="P95">
-        <v>44.03217</v>
+        <v>34.84202</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.25">
@@ -5960,43 +5960,43 @@
         <v>1</v>
       </c>
       <c r="D96">
-        <v>88.7</v>
+        <v>134.3</v>
       </c>
       <c r="E96">
-        <v>0.4075</v>
+        <v>-0.2673</v>
       </c>
       <c r="F96">
-        <v>0.36</v>
+        <v>-0.36</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>-0.14887598630342194</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>-0.20000000000001705</v>
       </c>
       <c r="I96">
-        <v>4.9339</v>
+        <v>1.21964</v>
       </c>
       <c r="J96">
-        <v>-1.63753</v>
+        <v>4.14916</v>
       </c>
       <c r="K96">
-        <v>3.42019</v>
+        <v>11.93582</v>
       </c>
       <c r="L96">
-        <v>0.83146</v>
+        <v>12.71909</v>
       </c>
       <c r="M96">
-        <v>14.65213</v>
+        <v>10.46172</v>
       </c>
       <c r="N96">
-        <v>22.69124</v>
+        <v>19.39668</v>
       </c>
       <c r="O96">
-        <v>23.87463</v>
+        <v>12.88563</v>
       </c>
       <c r="P96">
-        <v>31.12721</v>
+        <v>23.54346</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.25">
@@ -6010,43 +6010,43 @@
         <v>1</v>
       </c>
       <c r="D97">
-        <v>356.83</v>
+        <v>43.47</v>
       </c>
       <c r="E97">
-        <v>0.3882</v>
+        <v>-0.3896</v>
       </c>
       <c r="F97">
-        <v>1.38</v>
+        <v>-0.17</v>
       </c>
       <c r="G97">
-        <v>0</v>
+        <v>-0.011500862564698235</v>
       </c>
       <c r="H97">
-        <v>0</v>
+        <v>-0.005000000000002558</v>
       </c>
       <c r="I97">
-        <v>6.02121</v>
+        <v>0.62298</v>
       </c>
       <c r="J97">
-        <v>0.65516</v>
+        <v>-3.08889</v>
       </c>
       <c r="K97">
-        <v>5.54415</v>
+        <v>-2.41665</v>
       </c>
       <c r="L97">
-        <v>6.36402</v>
+        <v>1.01923</v>
       </c>
       <c r="M97">
-        <v>10.48076</v>
+        <v>10.71338</v>
       </c>
       <c r="N97">
-        <v>21.46948</v>
+        <v>17.0097</v>
       </c>
       <c r="O97">
-        <v>20.51774</v>
+        <v>13.30216</v>
       </c>
       <c r="P97">
-        <v>25.41957</v>
+        <v>23.8053</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.25">
@@ -6060,43 +6060,43 @@
         <v>1</v>
       </c>
       <c r="D98">
-        <v>28.55</v>
+        <v>288.75</v>
       </c>
       <c r="E98">
-        <v>0.3868</v>
+        <v>-0.3898</v>
       </c>
       <c r="F98">
-        <v>0.11</v>
+        <v>-1.13</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>0.29175784099196794</v>
       </c>
       <c r="H98">
-        <v>0</v>
+        <v>0.839999999999975</v>
       </c>
       <c r="I98">
-        <v>-2.31843</v>
+        <v>7.31811</v>
       </c>
       <c r="J98">
-        <v>7.46569</v>
+        <v>6.38567</v>
       </c>
       <c r="K98">
-        <v>2.33846</v>
+        <v>5.37856</v>
       </c>
       <c r="L98">
-        <v>-1.81976</v>
+        <v>10.99375</v>
       </c>
       <c r="M98">
-        <v>22.40648</v>
+        <v>31.56789</v>
       </c>
       <c r="N98">
-        <v>27.54754</v>
+        <v>28.15166</v>
       </c>
       <c r="O98">
-        <v>28.11438</v>
+        <v>29.28016</v>
       </c>
       <c r="P98">
-        <v>35.44407</v>
+        <v>41.23238</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.25">
@@ -6110,43 +6110,43 @@
         <v>1</v>
       </c>
       <c r="D99">
-        <v>108.85</v>
+        <v>84.24</v>
       </c>
       <c r="E99">
-        <v>0.3827</v>
+        <v>-0.9372</v>
       </c>
       <c r="F99">
-        <v>0.415</v>
+        <v>-0.797</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>0.8634550110164882</v>
       </c>
       <c r="H99">
-        <v>0</v>
+        <v>0.7249999999999943</v>
       </c>
       <c r="I99">
-        <v>-2.05663</v>
+        <v>5.655</v>
       </c>
       <c r="J99">
-        <v>0.47501</v>
+        <v>-4.98544</v>
       </c>
       <c r="K99">
-        <v>4.61438</v>
+        <v>-3.47056</v>
       </c>
       <c r="L99">
-        <v>6.18166</v>
+        <v>6.20165</v>
       </c>
       <c r="M99">
-        <v>14.82047</v>
+        <v>52.764</v>
       </c>
       <c r="N99">
-        <v>19.46418</v>
+        <v>88.77516</v>
       </c>
       <c r="O99">
-        <v>19.88633</v>
+        <v>80.12651</v>
       </c>
       <c r="P99">
-        <v>22.44841</v>
+        <v>149.09025</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.25">
@@ -6160,43 +6160,43 @@
         <v>1</v>
       </c>
       <c r="D100">
-        <v>73.919</v>
+        <v>88.33</v>
       </c>
       <c r="E100">
-        <v>0.3783</v>
+        <v>-0.4171</v>
       </c>
       <c r="F100">
-        <v>0.2786</v>
+        <v>-0.37</v>
       </c>
       <c r="G100">
-        <v>0</v>
+        <v>-0.05657388549445254</v>
       </c>
       <c r="H100">
-        <v>0</v>
+        <v>-0.04999999999999716</v>
       </c>
       <c r="I100">
-        <v>2.87656</v>
+        <v>2.2253</v>
       </c>
       <c r="J100">
-        <v>1.62877</v>
+        <v>-0.71669</v>
       </c>
       <c r="K100">
-        <v>3.22409</v>
+        <v>3.14099</v>
       </c>
       <c r="L100">
-        <v>3.74714</v>
+        <v>2.62832</v>
       </c>
       <c r="M100">
-        <v>8.46858</v>
+        <v>10.65735</v>
       </c>
       <c r="N100">
-        <v>15.20927</v>
+        <v>24.08196</v>
       </c>
       <c r="O100">
-        <v>12.4242</v>
+        <v>23.54021</v>
       </c>
       <c r="P100">
-        <v>21.10881</v>
+        <v>30.62001</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.25">
@@ -6210,13 +6210,13 @@
         <v>1</v>
       </c>
       <c r="D101">
-        <v>126.88</v>
+        <v>43.67</v>
       </c>
       <c r="E101">
-        <v>0.3639</v>
+        <v>-0.4559</v>
       </c>
       <c r="F101">
-        <v>0.46</v>
+        <v>-0.2</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -6225,28 +6225,28 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>1.68333</v>
+        <v>3.38462</v>
       </c>
       <c r="J101">
-        <v>2.96755</v>
+        <v>6.84932</v>
       </c>
       <c r="K101">
-        <v>6.67335</v>
+        <v>6.04974</v>
       </c>
       <c r="L101">
-        <v>6.25281</v>
+        <v>5.01964</v>
       </c>
       <c r="M101">
-        <v>14.34488</v>
+        <v>7.40309</v>
       </c>
       <c r="N101">
-        <v>31.33418</v>
+        <v>26.99839</v>
       </c>
       <c r="O101">
-        <v>25.56119</v>
+        <v>16.67123</v>
       </c>
       <c r="P101">
-        <v>39.43178</v>
+        <v>32.70342</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.25">
@@ -6260,43 +6260,43 @@
         <v>1</v>
       </c>
       <c r="D102">
-        <v>43.6</v>
+        <v>34.84</v>
       </c>
       <c r="E102">
-        <v>0.3591</v>
+        <v>-0.4856</v>
       </c>
       <c r="F102">
-        <v>0.156</v>
+        <v>-0.17</v>
       </c>
       <c r="G102">
-        <v>0</v>
+        <v>-0.0034433285509449314</v>
       </c>
       <c r="H102">
-        <v>0</v>
+        <v>-0.0012000000000043087</v>
       </c>
       <c r="I102">
-        <v>1.55597</v>
+        <v>1.48256</v>
       </c>
       <c r="J102">
-        <v>-4.91411</v>
+        <v>6.69315</v>
       </c>
       <c r="K102">
-        <v>-2.14813</v>
+        <v>7.04425</v>
       </c>
       <c r="L102">
-        <v>-0.34184</v>
+        <v>5.86233</v>
       </c>
       <c r="M102">
-        <v>13.90987</v>
+        <v>8.8713</v>
       </c>
       <c r="N102">
-        <v>17.05097</v>
+        <v>24.49009</v>
       </c>
       <c r="O102">
-        <v>13.61393</v>
+        <v>17.53356</v>
       </c>
       <c r="P102">
-        <v>23.90145</v>
+        <v>30.35225</v>
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.25">
@@ -6310,43 +6310,43 @@
         <v>1</v>
       </c>
       <c r="D103">
-        <v>44.0149</v>
+        <v>230.12</v>
       </c>
       <c r="E103">
-        <v>0.3378</v>
+        <v>-0.4757</v>
       </c>
       <c r="F103">
-        <v>0.1482</v>
+        <v>-1.1</v>
       </c>
       <c r="G103">
-        <v>-0.00022719527434583587</v>
+        <v>-0.008690362388103681</v>
       </c>
       <c r="H103">
-        <v>-0.00010000000000331966</v>
+        <v>-0.01999999999998181</v>
       </c>
       <c r="I103">
-        <v>0.86957</v>
+        <v>0.3864</v>
       </c>
       <c r="J103">
-        <v>-0.1343</v>
+        <v>0.45618</v>
       </c>
       <c r="K103">
-        <v>1.90803</v>
+        <v>3.0063</v>
       </c>
       <c r="L103">
-        <v>1.1862</v>
+        <v>1.07149</v>
       </c>
       <c r="M103">
-        <v>5.7637</v>
+        <v>-2.37148</v>
       </c>
       <c r="N103">
-        <v>20.64451</v>
+        <v>12.38594</v>
       </c>
       <c r="O103">
-        <v>14.29052</v>
+        <v>10.70546</v>
       </c>
       <c r="P103">
-        <v>30.96996</v>
+        <v>6.43534</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.25">
@@ -6360,43 +6360,43 @@
         <v>1</v>
       </c>
       <c r="D104">
-        <v>54.26</v>
+        <v>78.51</v>
       </c>
       <c r="E104">
-        <v>0.3143</v>
+        <v>-0.4754</v>
       </c>
       <c r="F104">
-        <v>0.17</v>
+        <v>-0.375</v>
       </c>
       <c r="G104">
-        <v>0</v>
+        <v>-0.02547121752419259</v>
       </c>
       <c r="H104">
-        <v>0</v>
+        <v>-0.01999999999999602</v>
       </c>
       <c r="I104">
-        <v>3.23811</v>
+        <v>1.8934</v>
       </c>
       <c r="J104">
-        <v>4.8944</v>
+        <v>3.65435</v>
       </c>
       <c r="K104">
-        <v>7.29774</v>
+        <v>5.01472</v>
       </c>
       <c r="L104">
-        <v>9.64697</v>
+        <v>5.05647</v>
       </c>
       <c r="M104">
-        <v>12.97416</v>
+        <v>10.8764</v>
       </c>
       <c r="N104">
-        <v>25.86849</v>
+        <v>29.48126</v>
       </c>
       <c r="O104">
-        <v>19.25146</v>
+        <v>21.89801</v>
       </c>
       <c r="P104">
-        <v>35.43759</v>
+        <v>38.2987</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.25">
@@ -6410,13 +6410,13 @@
         <v>1</v>
       </c>
       <c r="D105">
-        <v>61.13</v>
+        <v>37.88</v>
       </c>
       <c r="E105">
-        <v>0.3118</v>
+        <v>-0.4991</v>
       </c>
       <c r="F105">
-        <v>0.19</v>
+        <v>-0.19</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -6425,28 +6425,28 @@
         <v>0</v>
       </c>
       <c r="I105">
-        <v>2.32259</v>
+        <v>3.65267</v>
       </c>
       <c r="J105">
-        <v>-1.41528</v>
+        <v>3.39879</v>
       </c>
       <c r="K105">
-        <v>0.47045</v>
+        <v>6.96203</v>
       </c>
       <c r="L105">
-        <v>-2.10682</v>
+        <v>5.97113</v>
       </c>
       <c r="M105">
-        <v>7.47427</v>
+        <v>12.03339</v>
       </c>
       <c r="N105">
-        <v>18.54071</v>
+        <v>27.79353</v>
       </c>
       <c r="O105">
-        <v>17.45913</v>
+        <v>24.00519</v>
       </c>
       <c r="P105">
-        <v>22.69142</v>
+        <v>38.47883</v>
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.25">
@@ -6460,43 +6460,43 @@
         <v>1</v>
       </c>
       <c r="D106">
-        <v>63.35</v>
+        <v>39.95</v>
       </c>
       <c r="E106">
-        <v>0.3008</v>
+        <v>-0.4808</v>
       </c>
       <c r="F106">
-        <v>0.19</v>
+        <v>-0.193</v>
       </c>
       <c r="G106">
-        <v>0</v>
+        <v>0.03757515030060262</v>
       </c>
       <c r="H106">
-        <v>0</v>
+        <v>0.015000000000000568</v>
       </c>
       <c r="I106">
-        <v>5.05951</v>
+        <v>1.99951</v>
       </c>
       <c r="J106">
-        <v>4.60107</v>
+        <v>3.60302</v>
       </c>
       <c r="K106">
-        <v>11.07379</v>
+        <v>5.87364</v>
       </c>
       <c r="L106">
-        <v>11.44559</v>
+        <v>7.59879</v>
       </c>
       <c r="M106">
-        <v>15.30997</v>
+        <v>10.02844</v>
       </c>
       <c r="N106">
-        <v>25.51577</v>
+        <v>29.95613</v>
       </c>
       <c r="O106">
-        <v>18.72991</v>
+        <v>19.00569</v>
       </c>
       <c r="P106">
-        <v>33.52105</v>
+        <v>37.77196</v>
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.25">
@@ -6510,43 +6510,43 @@
         <v>1</v>
       </c>
       <c r="D107">
-        <v>215.21</v>
+        <v>110.33</v>
       </c>
       <c r="E107">
-        <v>0.2936</v>
+        <v>-0.5185</v>
       </c>
       <c r="F107">
-        <v>0.63</v>
+        <v>-0.575</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>0.03626802067276457</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>0.03999999999999204</v>
       </c>
       <c r="I107">
-        <v>8.48687</v>
+        <v>1.27563</v>
       </c>
       <c r="J107">
-        <v>-0.18045</v>
+        <v>2.50462</v>
       </c>
       <c r="K107">
-        <v>-4.05798</v>
+        <v>6.77056</v>
       </c>
       <c r="L107">
-        <v>-4.43031</v>
+        <v>7.73768</v>
       </c>
       <c r="M107">
-        <v>34.94971</v>
+        <v>11.86758</v>
       </c>
       <c r="N107">
-        <v>44.74741</v>
+        <v>25.9711</v>
       </c>
       <c r="O107">
-        <v>42.18641</v>
+        <v>22.7397</v>
       </c>
       <c r="P107">
-        <v>78.44583</v>
+        <v>35.44198</v>
       </c>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.25">
@@ -6560,43 +6560,43 @@
         <v>1</v>
       </c>
       <c r="D108">
-        <v>42.0261</v>
+        <v>41.5</v>
       </c>
       <c r="E108">
-        <v>0.255</v>
+        <v>-0.5273</v>
       </c>
       <c r="F108">
-        <v>0.1069</v>
+        <v>-0.22</v>
       </c>
       <c r="G108">
-        <v>0.0002379479369823781</v>
+        <v>0</v>
       </c>
       <c r="H108">
-        <v>0.00009999999999621423</v>
+        <v>0</v>
       </c>
       <c r="I108">
-        <v>1.82485</v>
+        <v>1.91104</v>
       </c>
       <c r="J108">
-        <v>1.51499</v>
+        <v>-2.05456</v>
       </c>
       <c r="K108">
-        <v>3.09663</v>
+        <v>-0.3706</v>
       </c>
       <c r="L108">
-        <v>3.54837</v>
+        <v>-1.46886</v>
       </c>
       <c r="M108">
-        <v>7.76567</v>
+        <v>9.62374</v>
       </c>
       <c r="N108">
-        <v>12.57076</v>
+        <v>22.43899</v>
       </c>
       <c r="O108">
-        <v>9.87326</v>
+        <v>20.29861</v>
       </c>
       <c r="P108">
-        <v>17.26639</v>
+        <v>36.68232</v>
       </c>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.25">
@@ -6610,43 +6610,43 @@
         <v>1</v>
       </c>
       <c r="D109">
-        <v>37.33</v>
+        <v>79.1183</v>
       </c>
       <c r="E109">
-        <v>0.2417</v>
+        <v>-0.6467</v>
       </c>
       <c r="F109">
-        <v>0.09</v>
+        <v>-0.515</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>0.10996233474051835</v>
       </c>
       <c r="H109">
-        <v>0</v>
+        <v>0.0870000000000033</v>
       </c>
       <c r="I109">
-        <v>1.69445</v>
+        <v>4.3324</v>
       </c>
       <c r="J109">
-        <v>1.50027</v>
+        <v>5.12601</v>
       </c>
       <c r="K109">
-        <v>2.87531</v>
+        <v>5.36418</v>
       </c>
       <c r="L109">
-        <v>3.41857</v>
+        <v>2.79901</v>
       </c>
       <c r="M109">
-        <v>7.60555</v>
+        <v>6.27566</v>
       </c>
       <c r="N109">
-        <v>10.97525</v>
+        <v>23.04374</v>
       </c>
       <c r="O109">
-        <v>8.61062</v>
+        <v>15.37221</v>
       </c>
       <c r="P109">
-        <v>14.98764</v>
+        <v>26.87381</v>
       </c>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.25">
@@ -6660,13 +6660,13 @@
         <v>1</v>
       </c>
       <c r="D110">
-        <v>38</v>
+        <v>83.945</v>
       </c>
       <c r="E110">
-        <v>0.2242</v>
+        <v>-0.5956</v>
       </c>
       <c r="F110">
-        <v>0.085</v>
+        <v>-0.503</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -6675,28 +6675,28 @@
         <v>0</v>
       </c>
       <c r="I110">
-        <v>2.23144</v>
+        <v>0.88742</v>
       </c>
       <c r="J110">
-        <v>4.37441</v>
+        <v>4.19209</v>
       </c>
       <c r="K110">
-        <v>8.49131</v>
+        <v>5.2854</v>
       </c>
       <c r="L110">
-        <v>6.97643</v>
+        <v>5.70417</v>
       </c>
       <c r="M110">
-        <v>9.9511</v>
+        <v>7.01822</v>
       </c>
       <c r="N110">
-        <v>27.97259</v>
+        <v>18.77868</v>
       </c>
       <c r="O110">
-        <v>21.99766</v>
+        <v>14.4813</v>
       </c>
       <c r="P110">
-        <v>39.30731</v>
+        <v>23.03237</v>
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.25">
@@ -6710,43 +6710,43 @@
         <v>1</v>
       </c>
       <c r="D111">
-        <v>74.3411</v>
+        <v>45.18</v>
       </c>
       <c r="E111">
-        <v>0.2054</v>
+        <v>-0.5976</v>
       </c>
       <c r="F111">
-        <v>0.1524</v>
+        <v>-0.2716</v>
       </c>
       <c r="G111">
-        <v>0.00013451527421385194</v>
+        <v>-0.5984335122766842</v>
       </c>
       <c r="H111">
-        <v>0.00010000000000331966</v>
+        <v>-0.27199999999999847</v>
       </c>
       <c r="I111">
-        <v>0.08036</v>
+        <v>3.0839</v>
       </c>
       <c r="J111">
-        <v>5.3136</v>
+        <v>2.63396</v>
       </c>
       <c r="K111">
-        <v>8.00444</v>
+        <v>9.17052</v>
       </c>
       <c r="L111">
-        <v>8.42567</v>
+        <v>9.1531</v>
       </c>
       <c r="M111">
-        <v>10.05176</v>
+        <v>12.98182</v>
       </c>
       <c r="N111">
-        <v>26.69872</v>
+        <v>25.28433</v>
       </c>
       <c r="O111">
-        <v>17.75452</v>
+        <v>22.01354</v>
       </c>
       <c r="P111">
-        <v>36.37396</v>
+        <v>36.83872</v>
       </c>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.25">
@@ -6760,43 +6760,43 @@
         <v>1</v>
       </c>
       <c r="D112">
-        <v>44.6</v>
+        <v>102.43</v>
       </c>
       <c r="E112">
-        <v>0.2022</v>
+        <v>-0.6402</v>
       </c>
       <c r="F112">
-        <v>0.09</v>
+        <v>-0.66</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>0.14665623777865242</v>
       </c>
       <c r="H112">
-        <v>0</v>
+        <v>0.15000000000000568</v>
       </c>
       <c r="I112">
-        <v>1.78408</v>
+        <v>7.25398</v>
       </c>
       <c r="J112">
-        <v>2.60549</v>
+        <v>0.34536</v>
       </c>
       <c r="K112">
-        <v>7.79126</v>
+        <v>3.06492</v>
       </c>
       <c r="L112">
-        <v>4.97468</v>
+        <v>8.67767</v>
       </c>
       <c r="M112">
-        <v>5.60849</v>
+        <v>46.52536</v>
       </c>
       <c r="N112">
-        <v>20.02391</v>
+        <v>65.94575</v>
       </c>
       <c r="O112">
-        <v>16.69035</v>
+        <v>61.31478</v>
       </c>
       <c r="P112">
-        <v>24.21511</v>
+        <v>76.62667</v>
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.25">
@@ -6810,43 +6810,43 @@
         <v>1</v>
       </c>
       <c r="D113">
-        <v>50.27</v>
+        <v>53.35</v>
       </c>
       <c r="E113">
-        <v>0.1993</v>
+        <v>-0.6529</v>
       </c>
       <c r="F113">
-        <v>0.1</v>
+        <v>-0.3506</v>
       </c>
       <c r="G113">
-        <v>0</v>
+        <v>-0.0936329588014928</v>
       </c>
       <c r="H113">
-        <v>0</v>
+        <v>-0.04999999999999716</v>
       </c>
       <c r="I113">
-        <v>4.02225</v>
+        <v>3.10979</v>
       </c>
       <c r="J113">
-        <v>1.67826</v>
+        <v>5.47807</v>
       </c>
       <c r="K113">
-        <v>6.82115</v>
+        <v>6.60673</v>
       </c>
       <c r="L113">
-        <v>10.21551</v>
+        <v>5.62189</v>
       </c>
       <c r="M113">
-        <v>12.49753</v>
+        <v>6.56332</v>
       </c>
       <c r="N113">
-        <v>18.99175</v>
+        <v>24.40059</v>
       </c>
       <c r="O113">
-        <v>16.0519</v>
+        <v>15.36335</v>
       </c>
       <c r="P113">
-        <v>28.0156</v>
+        <v>28.1206</v>
       </c>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.25">
@@ -6860,43 +6860,43 @@
         <v>1</v>
       </c>
       <c r="D114">
-        <v>231.22</v>
+        <v>35.67</v>
       </c>
       <c r="E114">
-        <v>0.1863</v>
+        <v>-0.5576</v>
       </c>
       <c r="F114">
-        <v>0.43</v>
+        <v>-0.2</v>
       </c>
       <c r="G114">
-        <v>0</v>
+        <v>-0.07631874298541122</v>
       </c>
       <c r="H114">
-        <v>0</v>
+        <v>-0.027200000000000557</v>
       </c>
       <c r="I114">
-        <v>-2.02127</v>
+        <v>2.00918</v>
       </c>
       <c r="J114">
-        <v>0.26017</v>
+        <v>2.27338</v>
       </c>
       <c r="K114">
-        <v>3.0063</v>
+        <v>3.05462</v>
       </c>
       <c r="L114">
-        <v>0.71241</v>
+        <v>2.46506</v>
       </c>
       <c r="M114">
-        <v>-1.05726</v>
+        <v>8.48512</v>
       </c>
       <c r="N114">
-        <v>12.99641</v>
+        <v>25.66684</v>
       </c>
       <c r="O114">
-        <v>10.70546</v>
+        <v>17.95122</v>
       </c>
       <c r="P114">
-        <v>8.83739</v>
+        <v>34.08203</v>
       </c>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.25">
@@ -6910,43 +6910,43 @@
         <v>1</v>
       </c>
       <c r="D115">
-        <v>40.1997</v>
+        <v>20.36</v>
       </c>
       <c r="E115">
-        <v>0.1487</v>
+        <v>-0.6829</v>
       </c>
       <c r="F115">
-        <v>0.0597</v>
+        <v>-0.14</v>
       </c>
       <c r="G115">
-        <v>-0.0007462686567235162</v>
+        <v>0</v>
       </c>
       <c r="H115">
-        <v>-0.00030000000000285354</v>
+        <v>0</v>
       </c>
       <c r="I115">
-        <v>2.02107</v>
+        <v>1.94708</v>
       </c>
       <c r="J115">
-        <v>1.69427</v>
+        <v>8.32891</v>
       </c>
       <c r="K115">
-        <v>3.28055</v>
+        <v>9.59185</v>
       </c>
       <c r="L115">
-        <v>3.67073</v>
+        <v>9.13735</v>
       </c>
       <c r="M115">
-        <v>8.36493</v>
+        <v>13.89221</v>
       </c>
       <c r="N115">
-        <v>11.97412</v>
+        <v>31.72161</v>
       </c>
       <c r="O115">
-        <v>9.54236</v>
+        <v>20.79477</v>
       </c>
       <c r="P115">
-        <v>16.30477</v>
+        <v>36.40151</v>
       </c>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.25">
@@ -6960,43 +6960,43 @@
         <v>1</v>
       </c>
       <c r="D116">
-        <v>110.63</v>
+        <v>77.47</v>
       </c>
       <c r="E116">
-        <v>0.142</v>
+        <v>-0.7049</v>
       </c>
       <c r="F116">
-        <v>0.1569</v>
+        <v>-0.55</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>-0.05160624435557509</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>-0.04000000000000625</v>
       </c>
       <c r="I116">
-        <v>1.87574</v>
+        <v>22.05007</v>
       </c>
       <c r="J116">
-        <v>2.53526</v>
+        <v>19.22824</v>
       </c>
       <c r="K116">
-        <v>7.30505</v>
+        <v>13.97665</v>
       </c>
       <c r="L116">
-        <v>7.97397</v>
+        <v>-1.61653</v>
       </c>
       <c r="M116">
-        <v>15.49925</v>
+        <v>-5.38872</v>
       </c>
       <c r="N116">
-        <v>26.8785</v>
+        <v>27.36466</v>
       </c>
       <c r="O116">
-        <v>23.35413</v>
+        <v>6.26147</v>
       </c>
       <c r="P116">
-        <v>36.19948</v>
+        <v>59.81405</v>
       </c>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.25">
@@ -7010,43 +7010,43 @@
         <v>1</v>
       </c>
       <c r="D117">
-        <v>99.8949</v>
+        <v>44.54</v>
       </c>
       <c r="E117">
-        <v>0.0951</v>
+        <v>-0.7355</v>
       </c>
       <c r="F117">
-        <v>0.0949</v>
+        <v>-0.33</v>
       </c>
       <c r="G117">
-        <v>-0.00010010511035498155</v>
+        <v>0.06740058413839843</v>
       </c>
       <c r="H117">
-        <v>-0.0000999999999891088</v>
+        <v>0.030000000000001137</v>
       </c>
       <c r="I117">
-        <v>-1.52925</v>
+        <v>13.68608</v>
       </c>
       <c r="J117">
-        <v>4.75618</v>
+        <v>6.55699</v>
       </c>
       <c r="K117">
-        <v>2.58009</v>
+        <v>-3.93379</v>
       </c>
       <c r="L117">
-        <v>0.58515</v>
+        <v>-21.0424</v>
       </c>
       <c r="M117">
-        <v>22.35961</v>
+        <v>-13.07139</v>
       </c>
       <c r="N117">
-        <v>28.07074</v>
+        <v>-1.08191</v>
       </c>
       <c r="O117">
-        <v>28.21783</v>
+        <v>4.34275</v>
       </c>
       <c r="P117">
-        <v>35.05145</v>
+        <v>15.46536</v>
       </c>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.25">
@@ -7060,43 +7060,43 @@
         <v>1</v>
       </c>
       <c r="D118">
-        <v>77.3498</v>
+        <v>58.21</v>
       </c>
       <c r="E118">
-        <v>0.0932</v>
+        <v>-0.801</v>
       </c>
       <c r="F118">
-        <v>0.072</v>
+        <v>-0.47</v>
       </c>
       <c r="G118">
-        <v>-0.0002585649644375287</v>
+        <v>-0.2741134144252126</v>
       </c>
       <c r="H118">
-        <v>-0.00019999999999242846</v>
+        <v>-0.1599999999999966</v>
       </c>
       <c r="I118">
-        <v>0.16787</v>
+        <v>3.2605</v>
       </c>
       <c r="J118">
-        <v>2.74172</v>
+        <v>1.272</v>
       </c>
       <c r="K118">
-        <v>6.00173</v>
+        <v>1.80625</v>
       </c>
       <c r="L118">
-        <v>9.59374</v>
+        <v>1.57909</v>
       </c>
       <c r="M118">
-        <v>9.93498</v>
+        <v>9.89161</v>
       </c>
       <c r="N118">
-        <v>21.42499</v>
+        <v>34.8859</v>
       </c>
       <c r="O118">
-        <v>15.73128</v>
+        <v>32.57628</v>
       </c>
       <c r="P118">
-        <v>29.06881</v>
+        <v>43.39237</v>
       </c>
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.25">
@@ -7110,43 +7110,43 @@
         <v>1</v>
       </c>
       <c r="D119">
-        <v>101.87</v>
+        <v>577.19</v>
       </c>
       <c r="E119">
-        <v>0.0786</v>
+        <v>-0.9779</v>
       </c>
       <c r="F119">
-        <v>0.08</v>
+        <v>-5.7</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>0.24140326502259468</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>1.3900000000001</v>
       </c>
       <c r="I119">
-        <v>2.3676</v>
+        <v>7.88651</v>
       </c>
       <c r="J119">
-        <v>2.74886</v>
+        <v>0.29077</v>
       </c>
       <c r="K119">
-        <v>7.75254</v>
+        <v>2.26495</v>
       </c>
       <c r="L119">
-        <v>8.02581</v>
+        <v>7.93845</v>
       </c>
       <c r="M119">
-        <v>16.21666</v>
+        <v>45.10829</v>
       </c>
       <c r="N119">
-        <v>27.34773</v>
+        <v>68.00946</v>
       </c>
       <c r="O119">
-        <v>22.92229</v>
+        <v>61.86721</v>
       </c>
       <c r="P119">
-        <v>35.22496</v>
+        <v>100.8001</v>
       </c>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.25">
@@ -7160,43 +7160,43 @@
         <v>1</v>
       </c>
       <c r="D120">
-        <v>42.77</v>
+        <v>27.98</v>
       </c>
       <c r="E120">
-        <v>0.0702</v>
+        <v>-1.1657</v>
       </c>
       <c r="F120">
-        <v>0.03</v>
+        <v>-0.33</v>
       </c>
       <c r="G120">
-        <v>0</v>
+        <v>0.0035741091532979093</v>
       </c>
       <c r="H120">
-        <v>0</v>
+        <v>0.0010000000000012221</v>
       </c>
       <c r="I120">
-        <v>1.67869</v>
+        <v>2.4293</v>
       </c>
       <c r="J120">
-        <v>1.42913</v>
+        <v>-0.31757</v>
       </c>
       <c r="K120">
-        <v>2.97292</v>
+        <v>-8.11847</v>
       </c>
       <c r="L120">
-        <v>3.3924</v>
+        <v>-4.94589</v>
       </c>
       <c r="M120">
-        <v>8.97367</v>
+        <v>16.11237</v>
       </c>
       <c r="N120">
-        <v>12.78225</v>
+        <v>31.56327</v>
       </c>
       <c r="O120">
-        <v>10.28728</v>
+        <v>34.57352</v>
       </c>
       <c r="P120">
-        <v>16.88877</v>
+        <v>50.90467</v>
       </c>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.25">
@@ -7210,43 +7210,43 @@
         <v>1</v>
       </c>
       <c r="D121">
-        <v>134.66</v>
+        <v>95.92</v>
       </c>
       <c r="E121">
-        <v>0.0669</v>
+        <v>-1.3778</v>
       </c>
       <c r="F121">
-        <v>0.09</v>
+        <v>-1.34</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>0.2090082558261081</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>0.20000000000000284</v>
       </c>
       <c r="I121">
-        <v>0.88854</v>
+        <v>9.23284</v>
       </c>
       <c r="J121">
-        <v>3.7979</v>
+        <v>0.46488</v>
       </c>
       <c r="K121">
-        <v>11.87259</v>
+        <v>1.12784</v>
       </c>
       <c r="L121">
-        <v>11.67154</v>
+        <v>10.77441</v>
       </c>
       <c r="M121">
-        <v>10.39932</v>
+        <v>53.76827</v>
       </c>
       <c r="N121">
-        <v>19.8575</v>
+        <v>78.34191</v>
       </c>
       <c r="O121">
-        <v>12.82186</v>
+        <v>74.75799</v>
       </c>
       <c r="P121">
-        <v>23.21132</v>
+        <v>120.19901</v>
       </c>
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.25">
@@ -7260,43 +7260,43 @@
         <v>1</v>
       </c>
       <c r="D122">
-        <v>163.6239</v>
+        <v>66.34</v>
       </c>
       <c r="E122">
-        <v>0.0452</v>
+        <v>-1.5435</v>
       </c>
       <c r="F122">
-        <v>0.0739</v>
+        <v>-1.04</v>
       </c>
       <c r="G122">
-        <v>-0.00006111572874597838</v>
+        <v>0</v>
       </c>
       <c r="H122">
-        <v>-0.00010000000000331966</v>
+        <v>0</v>
       </c>
       <c r="I122">
-        <v>4.57582</v>
+        <v>-0.72252</v>
       </c>
       <c r="J122">
-        <v>7.77758</v>
+        <v>-0.48649</v>
       </c>
       <c r="K122">
-        <v>10.85568</v>
+        <v>3.70857</v>
       </c>
       <c r="L122">
-        <v>9.13953</v>
+        <v>4.57793</v>
       </c>
       <c r="M122">
-        <v>13.6067</v>
+        <v>12.45621</v>
       </c>
       <c r="N122">
-        <v>14.84294</v>
+        <v>17.58349</v>
       </c>
       <c r="O122">
-        <v>11.33138</v>
+        <v>19.3639</v>
       </c>
       <c r="P122">
-        <v>10.238</v>
+        <v>22.89222</v>
       </c>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.25">
@@ -7310,43 +7310,43 @@
         <v>1</v>
       </c>
       <c r="D123">
-        <v>24.015</v>
+        <v>107.18</v>
       </c>
       <c r="E123">
-        <v>0.0208</v>
+        <v>-1.5523</v>
       </c>
       <c r="F123">
-        <v>0.005</v>
+        <v>-1.69</v>
       </c>
       <c r="G123">
-        <v>0</v>
+        <v>0.009330969487734549</v>
       </c>
       <c r="H123">
-        <v>0</v>
+        <v>0.010000000000005116</v>
       </c>
       <c r="I123">
-        <v>3.88769</v>
+        <v>-0.87195</v>
       </c>
       <c r="J123">
-        <v>-5.12821</v>
+        <v>-0.61332</v>
       </c>
       <c r="K123">
-        <v>-3.65746</v>
+        <v>3.83044</v>
       </c>
       <c r="L123">
-        <v>-6.64599</v>
+        <v>4.75359</v>
       </c>
       <c r="M123">
-        <v>0.02493</v>
+        <v>12.24805</v>
       </c>
       <c r="N123">
-        <v>6.37481</v>
+        <v>17.03007</v>
       </c>
       <c r="O123">
-        <v>-2.80178</v>
+        <v>18.98794</v>
       </c>
       <c r="P123">
-        <v>16.4179</v>
+        <v>22.23924</v>
       </c>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.25">
@@ -7360,13 +7360,13 @@
         <v>1</v>
       </c>
       <c r="D124">
-        <v>72.98</v>
+        <v>112.99</v>
       </c>
       <c r="E124">
-        <v>0.0069</v>
+        <v>-1.5938</v>
       </c>
       <c r="F124">
-        <v>0.005</v>
+        <v>-1.83</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -7375,28 +7375,28 @@
         <v>0</v>
       </c>
       <c r="I124">
-        <v>-3.06715</v>
+        <v>-0.89643</v>
       </c>
       <c r="J124">
-        <v>9.07709</v>
+        <v>-0.78896</v>
       </c>
       <c r="K124">
-        <v>-0.25028</v>
+        <v>4.2697</v>
       </c>
       <c r="L124">
-        <v>-5.97641</v>
+        <v>5.3329</v>
       </c>
       <c r="M124">
-        <v>24.98258</v>
+        <v>12.07962</v>
       </c>
       <c r="N124">
-        <v>40.49915</v>
+        <v>17.6524</v>
       </c>
       <c r="O124">
-        <v>35.74267</v>
+        <v>18.65694</v>
       </c>
       <c r="P124">
-        <v>52.21882</v>
+        <v>23.52696</v>
       </c>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.25">
@@ -7410,43 +7410,43 @@
         <v>1</v>
       </c>
       <c r="D125">
-        <v>38.4959</v>
+        <v>47.365</v>
       </c>
       <c r="E125">
-        <v>-1.4694</v>
+        <v>-1.6099</v>
       </c>
       <c r="F125">
-        <v>-0.5741</v>
+        <v>-0.775</v>
       </c>
       <c r="G125">
-        <v>-0.00025976724855392673</v>
+        <v>-0.16861629254926397</v>
       </c>
       <c r="H125">
-        <v>-0.00010000000000331966</v>
+        <v>-0.0799999999999983</v>
       </c>
       <c r="I125">
-        <v>-0.71156</v>
+        <v>3.18067</v>
       </c>
       <c r="J125">
-        <v>3.11128</v>
+        <v>5.59509</v>
       </c>
       <c r="K125">
-        <v>1.50688</v>
+        <v>8.82943</v>
       </c>
       <c r="L125">
-        <v>4.09341</v>
+        <v>10.1267</v>
       </c>
       <c r="M125">
-        <v>15.27877</v>
+        <v>7.21912</v>
       </c>
       <c r="N125">
-        <v>32.83454</v>
+        <v>28.54529</v>
       </c>
       <c r="O125">
-        <v>27.04261</v>
+        <v>22.59259</v>
       </c>
       <c r="P125">
-        <v>28.07037</v>
+        <v>38.0332</v>
       </c>
     </row>
   </sheetData>
